--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45966.22916666666</v>
+        <v>45966.33333333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45966.25</v>
+        <v>45966.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45966.33333333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.33333333334</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.375</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.5</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="16">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="18">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="M21" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>9.5</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>27</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>7.1</v>
+        <v>1.98</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>8.5</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>27</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="30">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.81</v>
+        <v>2.27</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="M32" t="n">
         <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.05</v>
+        <v>1.89</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.31</v>
+        <v>3.85</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="34">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="M34" t="n">
         <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>2.31</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4885,126 +4885,255 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="L36" t="n">
         <v>3.95</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M36" t="n">
         <v>3.35</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N36" t="n">
         <v>1.89</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="3" t="n">
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="22">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>27</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="M28" t="n">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>27</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.27</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,19 +4348,19 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.81</v>
+        <v>2.27</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
         <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N33" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.05</v>
+        <v>1.89</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>2.31</v>
+        <v>3.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="35">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>1.89</v>
+        <v>2.31</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5134,6 +5134,135 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK37"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="N15" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,19 +2929,19 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="23">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="M24" t="n">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="N24" t="n">
-        <v>9.5</v>
+        <v>27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.11</v>
+        <v>7.1</v>
       </c>
       <c r="M27" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>27</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,19 +4348,19 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="33">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.89</v>
+        <v>2.27</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="M35" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="36">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.95</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>1.89</v>
+        <v>3.45</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5226,43 +5226,172 @@
         <v>2.3</v>
       </c>
       <c r="Z37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z38" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3" t="n">
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="M24" t="n">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>27</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.35</v>
+        <v>7.1</v>
       </c>
       <c r="M25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>9.5</v>
+        <v>1.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.18</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="N26" t="n">
-        <v>3.05</v>
+        <v>9.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>7.1</v>
+        <v>1.11</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>27</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,14 +4668,14 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="M33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N33" t="n">
         <v>3.05</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
         <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>2.31</v>
+        <v>3.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5097,7 +5097,7 @@
         <v>2.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="M37" t="n">
         <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>3.45</v>
+        <v>2.31</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         <v>2.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.81</v>
+        <v>2.89</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,19 +2800,19 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,19 +2929,19 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>7.1</v>
+        <v>1.11</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.4</v>
+        <v>27</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>7.1</v>
       </c>
       <c r="M26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>9.5</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M27" t="n">
-        <v>8.5</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
-        <v>27</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,55 +4023,55 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.6</v>
       </c>
-      <c r="M28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,19 +4348,19 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.27</v>
+        <v>1.81</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="M36" t="n">
         <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>3.45</v>
+        <v>2.31</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5097,7 +5097,7 @@
         <v>2.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
         <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2.31</v>
+        <v>3.45</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         <v>2.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45966.33333333334</v>
+        <v>45966.22916666666</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45966.33333333334</v>
+        <v>45966.25</v>
       </c>
     </row>
     <row r="4">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45966.375</v>
+        <v>45966.33333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.33333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>5.16</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.95</v>
+        <v>4.05</v>
       </c>
       <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.47</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X9" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.17</v>
+        <v>4.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.94</v>
+        <v>2.47</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.89</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>1.37</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.48</v>
+        <v>2.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,19 +2800,19 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,19 +2929,19 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="23">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.18</v>
+        <v>3.14</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.11</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>27</v>
+        <v>3.37</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>7.1</v>
+        <v>2.04</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>3.29</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>1.52</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="O30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,19 +4348,19 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N36" t="n">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>2.93</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N37" t="n">
-        <v>3.45</v>
+        <v>2.24</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.14</v>
+        <v>1.53</v>
       </c>
       <c r="M24" t="n">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.03</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>4.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N25" t="n">
-        <v>3.37</v>
+        <v>1.52</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.29</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.9</v>
+        <v>2.04</v>
       </c>
       <c r="M27" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>1.52</v>
+        <v>3.29</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>3.14</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.04</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>3.37</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="N31" t="n">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3.28</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.94</v>
+        <v>3.67</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="35">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,14 +4926,14 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="M35" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N35" t="n">
         <v>3.3</v>
       </c>
-      <c r="N35" t="n">
-        <v>3.67</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.06</v>
+        <v>2.93</v>
       </c>
       <c r="M36" t="n">
         <v>3.02</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.93</v>
+        <v>4.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,135 +5263,6 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK37"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45966.22916666666</v>
+        <v>45966.33333333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45966.25</v>
+        <v>45966.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45966.33333333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.33333333334</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.375</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.5</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>1.76</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="19">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.9</v>
+        <v>3.14</v>
       </c>
       <c r="M25" t="n">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="N25" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.04</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>29</v>
+        <v>3.37</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.14</v>
+        <v>4.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.88</v>
+        <v>4.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.03</v>
+        <v>1.52</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="33">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.67</v>
+        <v>2.94</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="M35" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="36">
@@ -5143,126 +5143,255 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="L38" t="n">
         <v>4.15</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M38" t="n">
         <v>3.4</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N38" t="n">
         <v>1.93</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="Z38" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3" t="n">
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45966.33333333334</v>
+        <v>45966.22916666666</v>
       </c>
     </row>
     <row r="3">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45966.375</v>
+        <v>45966.33333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>5.16</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.95</v>
+        <v>4.05</v>
       </c>
       <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.47</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X8" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.17</v>
+        <v>4.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.94</v>
+        <v>2.47</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.76</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>5.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>2.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.82</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.89</v>
+        <v>1.76</v>
       </c>
       <c r="M19" t="n">
-        <v>2.84</v>
+        <v>3.28</v>
       </c>
       <c r="N19" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T19" t="n">
         <v>3.1</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.7</v>
+        <v>3.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,19 +2929,19 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.14</v>
+        <v>2.04</v>
       </c>
       <c r="M25" t="n">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="N25" t="n">
-        <v>2.03</v>
+        <v>3.29</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.04</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>29</v>
+        <v>3.37</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
-        <v>3.64</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.29</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>4.9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N28" t="n">
-        <v>3.37</v>
+        <v>1.52</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.9</v>
+        <v>3.14</v>
       </c>
       <c r="M29" t="n">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="N29" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.94</v>
+        <v>3.67</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="35">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,14 +4926,14 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="M35" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N35" t="n">
         <v>3.3</v>
       </c>
-      <c r="N35" t="n">
-        <v>3.67</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.06</v>
+        <v>3.77</v>
       </c>
       <c r="M37" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,135 +5263,6 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK37"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.375</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.5</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="O19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.37</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.85</v>
+        <v>1.76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="N22" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.04</v>
+        <v>2.89</v>
       </c>
       <c r="M23" t="n">
-        <v>14</v>
+        <v>2.84</v>
       </c>
       <c r="N23" t="n">
-        <v>29</v>
+        <v>2.68</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>2.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>1.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>4.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.77</v>
+        <v>1.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>3.29</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.37</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.9</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="N28" t="n">
-        <v>1.52</v>
+        <v>3.29</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>1.52</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.94</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N31" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>3.37</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.67</v>
+        <v>5.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,19 +4993,19 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="37">
@@ -5143,126 +5143,771 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45966.79166666666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45966.79166666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45966.8125</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="L42" t="n">
         <v>3.77</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M42" t="n">
         <v>3.21</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N42" t="n">
         <v>1.84</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="Z42" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3" t="n">
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.89</v>
+        <v>1.53</v>
       </c>
       <c r="M23" t="n">
-        <v>2.84</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.68</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,55 +3507,55 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
+        <v>6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.1</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.85</v>
+        <v>4.9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>1.52</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>3.37</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="M28" t="n">
-        <v>3.64</v>
+        <v>14</v>
       </c>
       <c r="N28" t="n">
-        <v>3.29</v>
+        <v>29</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.14</v>
+        <v>2.04</v>
       </c>
       <c r="M29" t="n">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>2.03</v>
+        <v>3.29</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>1.52</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="33">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="N34" t="n">
-        <v>5.8</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>6.2</v>
+        <v>3.67</v>
       </c>
       <c r="O35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,19 +4993,19 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="36">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="M37" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="N37" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,49 +5313,49 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>2.4</v>
       </c>
-      <c r="M38" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z38" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,522 +5392,6 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45966.79166666666</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Vasco da Gama</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
-        <v>45966.8125</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.53</v>
+        <v>3.14</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.14</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>2.03</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="M26" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="N26" t="n">
-        <v>1.52</v>
+        <v>29</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>4.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N27" t="n">
-        <v>3.37</v>
+        <v>1.52</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.04</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>29</v>
+        <v>3.37</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.29</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N33" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M34" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>2.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.64</v>
+        <v>2.84</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>2.68</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.04</v>
+        <v>2.85</v>
       </c>
       <c r="M26" t="n">
-        <v>14</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>29</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.9</v>
+        <v>2.35</v>
       </c>
       <c r="M27" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>1.52</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>4.9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N28" t="n">
-        <v>3.37</v>
+        <v>1.52</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>3.37</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.94</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.34</v>
+        <v>1.97</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="M34" t="n">
-        <v>3.08</v>
+        <v>3.88</v>
       </c>
       <c r="N34" t="n">
-        <v>2.94</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N35" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.93</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.24</v>
+        <v>6.2</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,19 +5122,19 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="38">
@@ -5272,126 +5272,771 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45966.79166666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45966.79166666666</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45966.8125</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="L43" t="n">
         <v>3.77</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M43" t="n">
         <v>3.21</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N43" t="n">
         <v>1.84</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="Z43" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="M25" t="n">
         <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.9</v>
+        <v>1.53</v>
       </c>
       <c r="M28" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.52</v>
+        <v>5.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>4.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N29" t="n">
-        <v>3.37</v>
+        <v>1.52</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>3.14</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>5.8</v>
+        <v>3.37</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>1.04</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>29</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.14</v>
+        <v>2.04</v>
       </c>
       <c r="M34" t="n">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>3.29</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M39" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.93</v>
+        <v>2.06</v>
       </c>
       <c r="M41" t="n">
         <v>3.02</v>
       </c>
       <c r="N41" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.06</v>
+        <v>2.93</v>
       </c>
       <c r="M42" t="n">
         <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3374,65 +3374,65 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="N28" t="n">
-        <v>5.8</v>
+        <v>1.52</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.94</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.9</v>
+        <v>3.14</v>
       </c>
       <c r="M29" t="n">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="N29" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>3.29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.14</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3.37</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.29</v>
+        <v>5.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M38" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N39" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3374,65 +3374,65 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
         <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.9</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="N28" t="n">
-        <v>1.52</v>
+        <v>3.29</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.14</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.03</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="M30" t="n">
-        <v>3.64</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>3.29</v>
+        <v>29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>3.37</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="M33" t="n">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="N33" t="n">
-        <v>29</v>
+        <v>1.52</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="N35" t="n">
-        <v>3.37</v>
+        <v>2.03</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="O2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="T2" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="22">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="M24" t="n">
-        <v>2.84</v>
+        <v>3.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="O24" t="n">
         <v>3.5</v>
@@ -3540,16 +3540,16 @@
         <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AA24" t="n">
         <v>4.7</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="N31" t="n">
-        <v>3.37</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.42</v>
+        <v>4.9</v>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>1.52</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.9</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.52</v>
+        <v>3.37</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.25</v>
+        <v>1.04</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="N34" t="n">
-        <v>3.15</v>
+        <v>29</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.14</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.03</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M39" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.06</v>
+        <v>2.93</v>
       </c>
       <c r="M41" t="n">
         <v>3.02</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.93</v>
+        <v>2.06</v>
       </c>
       <c r="M42" t="n">
         <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK43"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,22 +681,22 @@
         <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
@@ -708,7 +708,7 @@
         <v>3.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
         <v>1.91</v>
@@ -723,7 +723,7 @@
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1443,16 +1443,16 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
         <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
         <v>1.88</v>
@@ -1461,43 +1461,43 @@
         <v>4.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
         <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AA8" t="n">
         <v>4.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
         <v>1.76</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7</v>
+        <v>1.76</v>
       </c>
       <c r="M21" t="n">
-        <v>5.1</v>
+        <v>3.28</v>
       </c>
       <c r="N21" t="n">
-        <v>1.37</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>2.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>3.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3245,90 +3245,90 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="M22" t="n">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="O22" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.32</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.97</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.71</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,14 +3636,14 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N25" t="n">
         <v>2.35</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>1.04</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>29</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
-        <v>3.64</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.29</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>3.14</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.14</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>5.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.9</v>
+        <v>2.04</v>
       </c>
       <c r="M32" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="N32" t="n">
-        <v>1.52</v>
+        <v>3.29</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3.37</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="M34" t="n">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
-        <v>29</v>
+        <v>1.52</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="Z35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA35" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA35" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.97</v>
+        <v>1.34</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,19 +4993,19 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,19 +5122,19 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="38">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M39" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.94</v>
+        <v>3.67</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="40">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,14 +5571,14 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="M40" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N40" t="n">
         <v>3.3</v>
       </c>
-      <c r="N40" t="n">
-        <v>3.67</v>
-      </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.06</v>
+        <v>3.77</v>
       </c>
       <c r="M42" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,135 +5908,6 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.375</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2871,34 +2871,34 @@
         <v>1.47</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y19" t="n">
         <v>1.73</v>
@@ -2907,16 +2907,16 @@
         <v>2.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3000,34 +3000,34 @@
         <v>1.37</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="n">
         <v>1.5</v>
@@ -3042,10 +3042,10 @@
         <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3245,65 +3245,65 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.63</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.27</v>
-      </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="X22" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,19 +3316,19 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="23">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>2.53</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3639,58 +3639,58 @@
         <v>2.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.04</v>
+        <v>2.37</v>
       </c>
       <c r="M27" t="n">
-        <v>14</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>29</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.2</v>
+        <v>1.61</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>4.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N29" t="n">
-        <v>3.37</v>
+        <v>1.52</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>3.88</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.03</v>
+        <v>3.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>3.14</v>
       </c>
       <c r="M31" t="n">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>2.03</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>1.04</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>29</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.9</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1.52</v>
+        <v>3.37</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,19 +4993,19 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="36">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N37" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M38" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>3.37</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
@@ -720,7 +720,7 @@
         <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD2" t="n">
         <v>2.15</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="N19" t="n">
-        <v>1.47</v>
+        <v>3.08</v>
       </c>
       <c r="O19" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>5.1</v>
+        <v>3.47</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.9</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AA22" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.83</v>
+        <v>1.04</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>29</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.53</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.52</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.16</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.85</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.36</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.86</v>
-      </c>
       <c r="Z25" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.38</v>
+        <v>1.97</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,50 +3765,50 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z26" t="n">
         <v>2.1</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2</v>
-      </c>
       <c r="AA26" t="n">
         <v>0</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>3.14</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>2.03</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.9</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.52</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.14</v>
+        <v>1.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.03</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.64</v>
+        <v>2.96</v>
       </c>
       <c r="N32" t="n">
-        <v>3.29</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="M33" t="n">
-        <v>14</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>29</v>
+        <v>3.67</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>2.93</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="N34" t="n">
-        <v>3.37</v>
+        <v>2.24</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>3.02</v>
       </c>
       <c r="N35" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,780 +5134,6 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.75</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3" t="n">
-        <v>45966.79166666666</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Bragantino</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
-        <v>45966.79166666666</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Vasco da Gama</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
-        <v>45966.8125</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45966.22916666666</v>
+        <v>45966.33333333334</v>
       </c>
     </row>
     <row r="3">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45966.33333333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.375</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.5</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.38</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>8.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.47</v>
+        <v>5.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.64</v>
+        <v>3.11</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>2.71</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="M24" t="n">
-        <v>14</v>
+        <v>3.46</v>
       </c>
       <c r="N24" t="n">
-        <v>29</v>
+        <v>2.12</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>2.94</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>2.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>4.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.97</v>
+        <v>1.17</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.37</v>
+        <v>2.31</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="M28" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="N28" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>2.42</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.08</v>
+        <v>5.02</v>
       </c>
       <c r="N30" t="n">
-        <v>2.94</v>
+        <v>1.51</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.65</v>
+        <v>3.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,62 +4410,62 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>13</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>45</v>
       </c>
       <c r="O31" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="P31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>15</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U31" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.44</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.91</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="M32" t="n">
-        <v>2.96</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
+        <v>6</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2.75</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="M33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" t="n">
         <v>3.3</v>
       </c>
-      <c r="N33" t="n">
-        <v>3.67</v>
-      </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.93</v>
+        <v>1.56</v>
       </c>
       <c r="M34" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.24</v>
+        <v>6.1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="36">
@@ -5014,126 +5014,900 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>45966.79166666666</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45966.79166666666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45966.79166666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45966.8125</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="L42" t="n">
         <v>3.77</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M42" t="n">
         <v>3.21</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N42" t="n">
         <v>1.84</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
+      <c r="O42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y42" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="Z42" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="3" t="n">
+      <c r="AA42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,62 +2862,62 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.51</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>2.19</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>6.5</v>
+        <v>2.82</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>5.53</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>2.07</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>4.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>3.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.46</v>
+        <v>1.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.34</v>
+        <v>6.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.73</v>
+        <v>2.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
         <v>2.63</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.16</v>
+        <v>2.83</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>3.51</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.18</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,19 +3703,19 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="N26" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="O26" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
@@ -3789,37 +3789,37 @@
         <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U26" t="n">
         <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="Z26" t="n">
         <v>1.98</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>3.06</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.4</v>
       </c>
-      <c r="O27" t="n">
-        <v>2.49</v>
-      </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.32</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M28" t="n">
         <v>3.08</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.94</v>
-      </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>3.08</v>
       </c>
       <c r="O28" t="n">
-        <v>3.43</v>
+        <v>2.9</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.63</v>
+        <v>4.29</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>3.85</v>
+        <v>2.44</v>
       </c>
       <c r="T28" t="n">
-        <v>2.13</v>
+        <v>3.22</v>
       </c>
       <c r="U28" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="X28" t="n">
-        <v>5.75</v>
+        <v>2.68</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.16</v>
+        <v>3.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.18</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.42</v>
+        <v>4.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="N29" t="n">
-        <v>3.05</v>
+        <v>1.52</v>
       </c>
       <c r="O29" t="n">
-        <v>3.04</v>
+        <v>4.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.64</v>
+        <v>1.95</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="S29" t="n">
-        <v>2.69</v>
+        <v>4.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.89</v>
+        <v>2.01</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>3.05</v>
+        <v>7.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.96</v>
+        <v>2.75</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.59</v>
+        <v>1.17</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>3.14</v>
       </c>
       <c r="M30" t="n">
-        <v>5.02</v>
+        <v>3.88</v>
       </c>
       <c r="N30" t="n">
-        <v>1.51</v>
+        <v>2.03</v>
       </c>
       <c r="O30" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="U30" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
         <v>1.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.02</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>45</v>
+        <v>3.37</v>
       </c>
       <c r="O31" t="n">
-        <v>1.25</v>
+        <v>2.49</v>
       </c>
       <c r="P31" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z31" t="n">
         <v>2.1</v>
       </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.39</v>
-      </c>
       <c r="AA31" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.63</v>
+        <v>1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>11</v>
+        <v>1.73</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>3.29</v>
       </c>
       <c r="O32" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.22</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH32" t="n">
-        <v>2.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.07</v>
+        <v>1.04</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>29</v>
       </c>
       <c r="O33" t="n">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.79</v>
+        <v>11</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,62 +4797,62 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="P34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD34" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,77 +5055,77 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
         <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R36" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>2.45</v>
+        <v>2.79</v>
       </c>
       <c r="T36" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.32</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="37">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,34 +5184,34 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S37" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
         <v>1.06</v>
@@ -5220,13 +5220,13 @@
         <v>1.36</v>
       </c>
       <c r="X37" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA37" t="n">
         <v>4</v>
@@ -5235,10 +5235,10 @@
         <v>1.22</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S38" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="T38" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V38" t="n">
         <v>1.06</v>
       </c>
       <c r="W38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.36</v>
       </c>
-      <c r="X38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5451,13 +5451,13 @@
         <v>3.67</v>
       </c>
       <c r="O39" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="P39" t="n">
         <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R39" t="n">
         <v>1.4</v>
@@ -5496,7 +5496,7 @@
         <v>1.8</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
         <v>1.85</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,40 +5571,40 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.06</v>
+        <v>2.93</v>
       </c>
       <c r="M40" t="n">
         <v>3.02</v>
       </c>
       <c r="N40" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="P40" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="R40" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S40" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="T40" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U40" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X40" t="n">
         <v>2.7</v>
@@ -5616,10 +5616,10 @@
         <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC40" t="n">
         <v>1.95</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,40 +5700,40 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.93</v>
+        <v>2.06</v>
       </c>
       <c r="M41" t="n">
         <v>3.02</v>
       </c>
       <c r="N41" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="P41" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="R41" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.15</v>
-      </c>
       <c r="U41" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X41" t="n">
         <v>2.7</v>
@@ -5745,16 +5745,16 @@
         <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5841,13 +5841,13 @@
         <v>4.7</v>
       </c>
       <c r="P42" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R42" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S42" t="n">
         <v>2.45</v>
@@ -5862,7 +5862,7 @@
         <v>1.07</v>
       </c>
       <c r="W42" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X42" t="n">
         <v>2.65</v>
@@ -5880,7 +5880,7 @@
         <v>1.16</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD42" t="n">
         <v>1.7</v>
@@ -5899,7 +5899,7 @@
         <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1482,7 +1482,7 @@
         <v>2.49</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="Z8" t="n">
         <v>1.51</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>5.03</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
         <v>2.31</v>
@@ -2109,10 +2109,10 @@
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
         <v>1.31</v>
@@ -2124,19 +2124,19 @@
         <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AC13" t="n">
         <v>2.14</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,62 +2604,62 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>6.7</v>
       </c>
       <c r="O17" t="n">
-        <v>7.85</v>
+        <v>2.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
         <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="X17" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA17" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
         <v>1.41</v>
@@ -2760,16 +2760,16 @@
         <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
         <v>1.9</v>
@@ -2781,13 +2781,13 @@
         <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
         <v>2.64</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,37 +2862,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>6.7</v>
+        <v>1.45</v>
       </c>
       <c r="O19" t="n">
-        <v>2.33</v>
+        <v>7.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.9</v>
+        <v>2.13</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="T19" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
         <v>1.44</v>
@@ -2901,22 +2901,22 @@
         <v>2.43</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.34</v>
+        <v>4.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.19</v>
+        <v>1.08</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3000,28 +3000,28 @@
         <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.53</v>
+        <v>5.14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="S20" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="T20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="V20" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
         <v>1.7</v>
@@ -3030,22 +3030,22 @@
         <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O21" t="n">
-        <v>6.5</v>
+        <v>4.68</v>
       </c>
       <c r="P21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="AB21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.75</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD21" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,62 +3249,62 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O22" t="n">
-        <v>4.68</v>
+        <v>6.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.05</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA23" t="n">
         <v>4.6</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>3.47</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="X25" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.59</v>
+        <v>1.77</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,19 +3703,19 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="M26" t="n">
-        <v>3.47</v>
+        <v>3.28</v>
       </c>
       <c r="N26" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
         <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
@@ -3789,53 +3789,53 @@
         <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
         <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.27</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>3.08</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.99</v>
+        <v>4.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.08</v>
+        <v>3.37</v>
       </c>
       <c r="O28" t="n">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.29</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
         <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
-        <v>2.68</v>
+        <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="Z28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="29">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.9</v>
+        <v>2.04</v>
       </c>
       <c r="M29" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>1.52</v>
+        <v>3.29</v>
       </c>
       <c r="O29" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X29" t="n">
         <v>4.5</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>7.5</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.17</v>
+        <v>1.79</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>2.03</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
         <v>2.4</v>
@@ -4305,7 +4305,7 @@
         <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
         <v>1.69</v>
@@ -4326,10 +4326,10 @@
         <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC30" t="n">
         <v>1.4</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
-        <v>4.3</v>
+        <v>3.21</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>3.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.04</v>
+        <v>4.9</v>
       </c>
       <c r="M32" t="n">
-        <v>3.64</v>
+        <v>4.8</v>
       </c>
       <c r="N32" t="n">
-        <v>3.29</v>
+        <v>1.52</v>
       </c>
       <c r="O32" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="U32" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.2</v>
       </c>
-      <c r="X32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.79</v>
+        <v>1.17</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.04</v>
       </c>
-      <c r="M33" t="n">
-        <v>14</v>
-      </c>
-      <c r="N33" t="n">
-        <v>29</v>
-      </c>
-      <c r="O33" t="n">
+      <c r="W33" t="n">
         <v>1.25</v>
       </c>
-      <c r="P33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>15</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.06</v>
-      </c>
       <c r="X33" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>3.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4818,7 +4818,7 @@
         <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
         <v>2</v>
@@ -4830,7 +4830,7 @@
         <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X34" t="n">
         <v>5.75</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="N35" t="n">
-        <v>5.8</v>
+        <v>29</v>
       </c>
       <c r="O35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>15</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.05</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.04</v>
-      </c>
       <c r="AB35" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.85</v>
+        <v>2.63</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P36" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.52</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S36" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="T36" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X36" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA36" t="n">
         <v>3.44</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5193,13 +5193,13 @@
         <v>2.94</v>
       </c>
       <c r="O37" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
         <v>1.46</v>
@@ -5214,13 +5214,13 @@
         <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X37" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Y37" t="n">
         <v>2.13</v>
@@ -5229,7 +5229,7 @@
         <v>1.63</v>
       </c>
       <c r="AA37" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB37" t="n">
         <v>1.22</v>
@@ -5254,7 +5254,7 @@
         <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5331,16 +5331,16 @@
         <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U38" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
         <v>1.06</v>
@@ -5349,7 +5349,7 @@
         <v>1.4</v>
       </c>
       <c r="X38" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="Y38" t="n">
         <v>2.35</v>
@@ -5361,7 +5361,7 @@
         <v>4.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC38" t="n">
         <v>1.95</v>
@@ -5383,7 +5383,7 @@
         <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
         <v>2.7</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U39" t="n">
         <v>1.38</v>
@@ -5475,10 +5475,10 @@
         <v>1.04</v>
       </c>
       <c r="W39" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X39" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Y39" t="n">
         <v>1.92</v>
@@ -5490,10 +5490,10 @@
         <v>3.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD39" t="n">
         <v>1.82</v>
@@ -5512,7 +5512,7 @@
         <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5580,19 +5580,19 @@
         <v>2.24</v>
       </c>
       <c r="O40" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q40" t="n">
         <v>2.88</v>
       </c>
       <c r="R40" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="T40" t="n">
         <v>3.15</v>
@@ -5601,13 +5601,13 @@
         <v>1.32</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W40" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="X40" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Y40" t="n">
         <v>2.35</v>
@@ -5616,16 +5616,16 @@
         <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB40" t="n">
         <v>1.19</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5712,31 +5712,31 @@
         <v>2.85</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U41" t="n">
         <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X41" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Y41" t="n">
         <v>2.35</v>
@@ -5745,16 +5745,16 @@
         <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5838,13 +5838,13 @@
         <v>1.84</v>
       </c>
       <c r="O42" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P42" t="n">
         <v>1.95</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R42" t="n">
         <v>1.49</v>
@@ -5856,13 +5856,13 @@
         <v>3.2</v>
       </c>
       <c r="U42" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V42" t="n">
         <v>1.07</v>
       </c>
       <c r="W42" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="X42" t="n">
         <v>2.65</v>
@@ -5880,10 +5880,10 @@
         <v>1.16</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1482,7 +1482,7 @@
         <v>2.49</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Z8" t="n">
         <v>1.51</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>5.03</v>
       </c>
       <c r="O13" t="n">
         <v>2.31</v>
@@ -2109,10 +2109,10 @@
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U13" t="n">
         <v>1.31</v>
@@ -2121,16 +2121,16 @@
         <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
         <v>2.74</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AA13" t="n">
         <v>3.8</v>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Z16" t="n">
         <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>6.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U17" t="n">
         <v>1.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.47</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AA17" t="n">
-        <v>5.34</v>
+        <v>4.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC17" t="n">
         <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.7</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>4.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,77 +2862,77 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="N19" t="n">
-        <v>1.45</v>
+        <v>3.66</v>
       </c>
       <c r="O19" t="n">
-        <v>7.7</v>
+        <v>3.02</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.13</v>
+        <v>4.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="S19" t="n">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="W19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.44</v>
       </c>
-      <c r="X19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>10.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="P20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.71</v>
       </c>
-      <c r="Q20" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AA20" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.59</v>
+        <v>3.1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3120,58 +3120,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="O21" t="n">
-        <v>4.68</v>
+        <v>4.83</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q21" t="n">
         <v>2.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
         <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD21" t="n">
         <v>2</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>2.82</v>
       </c>
       <c r="AH21" t="n">
         <v>1.13</v>
@@ -3249,34 +3249,34 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O22" t="n">
         <v>7</v>
       </c>
-      <c r="M22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="O22" t="n">
-        <v>6.5</v>
-      </c>
       <c r="P22" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
         <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
@@ -3288,22 +3288,22 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AC22" t="n">
         <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>2.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="T23" t="n">
-        <v>3.58</v>
+        <v>3.09</v>
       </c>
       <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.25</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>2.05</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="24">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="M25" t="n">
-        <v>3.47</v>
+        <v>2.87</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="S25" t="n">
-        <v>2.89</v>
+        <v>2.27</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.77</v>
+        <v>2.59</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,19 +3703,19 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
         <v>1.31</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.06</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="U26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.4</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.99</v>
+        <v>4.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="M27" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.08</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.88</v>
+        <v>3.94</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="X27" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.61</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
         <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.37</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="29">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Z29" t="n">
         <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
         <v>1.79</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.14</v>
+        <v>2.49</v>
       </c>
       <c r="M30" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>4.1</v>
+        <v>2.59</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="X30" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>3.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.72</v>
+        <v>1.23</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>4.26</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1</v>
+        <v>6.15</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.01</v>
+        <v>2.31</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.79</v>
+        <v>3.12</v>
       </c>
       <c r="T31" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="X31" t="n">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.9</v>
+        <v>1.44</v>
       </c>
       <c r="M32" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.52</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="P32" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.95</v>
+        <v>6.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="T32" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.17</v>
+        <v>2.74</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U33" t="n">
         <v>1.53</v>
       </c>
-      <c r="M33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.85</v>
+        <v>2.49</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M34" t="n">
+        <v>16</v>
+      </c>
+      <c r="N34" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.42</v>
       </c>
-      <c r="M34" t="n">
-        <v>5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V34" t="n">
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.02</v>
       </c>
-      <c r="W34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH34" t="n">
-        <v>2.75</v>
+        <v>10</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>14</v>
+        <v>5.21</v>
       </c>
       <c r="N35" t="n">
-        <v>29</v>
+        <v>1.5</v>
       </c>
       <c r="O35" t="n">
-        <v>1.25</v>
+        <v>5.25</v>
       </c>
       <c r="P35" t="n">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>15</v>
+        <v>1.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="T35" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="U35" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AH35" t="n">
-        <v>10</v>
+        <v>1.15</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,62 +5055,62 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.28</v>
+        <v>4.09</v>
       </c>
       <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S36" t="n">
         <v>4</v>
       </c>
-      <c r="O36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD36" t="n">
         <v>2.8</v>
       </c>
-      <c r="U36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.06</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,86 +5184,86 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="M37" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="O37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S37" t="n">
         <v>3</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.55</v>
-      </c>
       <c r="T37" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="V37" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.4</v>
       </c>
-      <c r="X37" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="38">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M38" t="n">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T38" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V38" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X38" t="n">
         <v>2.75</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.67</v>
+        <v>3.05</v>
       </c>
       <c r="O39" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
         <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V39" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.3</v>
       </c>
-      <c r="X39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.93</v>
+        <v>1.86</v>
       </c>
       <c r="M40" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S40" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T40" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="U40" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V40" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O41" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="P41" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="T41" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V41" t="n">
         <v>1.06</v>
       </c>
       <c r="W41" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X41" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5788,126 +5788,255 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="L43" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O43" t="n">
         <v>4.4</v>
       </c>
-      <c r="P42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U42" t="n">
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U43" t="n">
         <v>1.32</v>
       </c>
-      <c r="V42" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W42" t="n">
+      <c r="V43" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W43" t="n">
         <v>1.39</v>
       </c>
-      <c r="X42" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z42" t="n">
+      <c r="X43" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z43" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD42" t="n">
+      <c r="AA43" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.75</v>
       </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AH43" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="n">
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK43"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45966.5</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>5.74</v>
+        <v>3.02</v>
       </c>
       <c r="P16" t="n">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>4.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.91</v>
+        <v>2.02</v>
       </c>
       <c r="T16" t="n">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="X16" t="n">
-        <v>3.58</v>
+        <v>2.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.88</v>
+        <v>7.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="O17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.26</v>
       </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.31</v>
-      </c>
       <c r="T17" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
         <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="O18" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="P18" t="n">
         <v>2.06</v>
@@ -2760,22 +2760,22 @@
         <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V18" t="n">
         <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AA18" t="n">
         <v>4.88</v>
@@ -2787,7 +2787,7 @@
         <v>2.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>2.75</v>
+        <v>4.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.66</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
-        <v>3.02</v>
+        <v>1.79</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.98</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="X19" t="n">
-        <v>2.04</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.14</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>3.2</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="N20" t="n">
-        <v>10.4</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>9</v>
+        <v>1.79</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>2.97</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.64</v>
+        <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="21">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>2.33</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.79</v>
+        <v>5.45</v>
       </c>
       <c r="R22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.25</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.1</v>
+        <v>2.05</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="M25" t="n">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X25" t="n">
         <v>3.5</v>
       </c>
-      <c r="P25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.6</v>
-      </c>
       <c r="Y25" t="n">
-        <v>2.59</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.24</v>
+        <v>1.68</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,19 +3703,19 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
         <v>1.31</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,62 +3765,62 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2.9</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.98</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>3.94</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.71</v>
+        <v>3.95</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.4</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X27" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="M28" t="n">
         <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
         <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="29">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>4.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.5</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>2.61</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.22</v>
       </c>
-      <c r="X29" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AH29" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.79</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.52</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>4.26</v>
+        <v>5.21</v>
       </c>
       <c r="N31" t="n">
-        <v>6.15</v>
+        <v>1.5</v>
       </c>
       <c r="O31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB31" t="n">
         <v>2</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.4</v>
+        <v>1.15</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="M32" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AC32" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.74</v>
+        <v>1.79</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>16</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>40.57</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="P33" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.7</v>
+        <v>13.48</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="U33" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.25</v>
+        <v>3.39</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>2.41</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.49</v>
+        <v>1.42</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.81</v>
+        <v>10</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="M34" t="n">
-        <v>16</v>
+        <v>4.26</v>
       </c>
       <c r="N34" t="n">
-        <v>40.57</v>
+        <v>6.15</v>
       </c>
       <c r="O34" t="n">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>2.31</v>
       </c>
       <c r="Q34" t="n">
-        <v>13.48</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3.12</v>
       </c>
       <c r="T34" t="n">
-        <v>1.71</v>
+        <v>2.95</v>
       </c>
       <c r="U34" t="n">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.39</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.48</v>
+        <v>3.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>10</v>
+        <v>2.4</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
-        <v>5.21</v>
+        <v>5.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
-        <v>5.25</v>
+        <v>1.8</v>
       </c>
       <c r="P35" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="T35" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.49</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AB35" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>1.18</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.15</v>
+        <v>2.74</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3.22</v>
       </c>
       <c r="N37" t="n">
-        <v>6.2</v>
+        <v>2.84</v>
       </c>
       <c r="O37" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="U37" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,19 +5251,19 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="38">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="T38" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V38" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
         <v>1.41</v>
       </c>
       <c r="X38" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA38" t="n">
-        <v>4</v>
+        <v>4.34</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>4.85</v>
       </c>
       <c r="R39" t="n">
         <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="T39" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="U39" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="X39" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.36</v>
+        <v>3.24</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="40">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,62 +5571,62 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.86</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M41" t="n">
         <v>3.1</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N41" t="n">
-        <v>2.2</v>
+        <v>3.38</v>
       </c>
       <c r="O41" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="P41" t="n">
         <v>1.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S41" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T41" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.36</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.34</v>
-      </c>
       <c r="X41" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.1</v>
+        <v>4.16</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="O42" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.05</v>
+        <v>2.66</v>
       </c>
       <c r="R42" t="n">
         <v>1.48</v>
       </c>
       <c r="S42" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="T42" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.33</v>
       </c>
-      <c r="V42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,135 +5908,6 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>5.03</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
@@ -2112,7 +2112,7 @@
         <v>2.54</v>
       </c>
       <c r="T13" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
         <v>1.31</v>
@@ -2127,10 +2127,10 @@
         <v>2.74</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
         <v>3.8</v>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>5.74</v>
+        <v>7.47</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,58 +2991,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="O20" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
         <v>2</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>2.85</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,58 +3120,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="N21" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.83</v>
+        <v>7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
         <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD21" t="n">
         <v>2</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>2.82</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>3.08</v>
       </c>
       <c r="O25" t="n">
-        <v>3.94</v>
+        <v>2.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.71</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="S25" t="n">
-        <v>2.89</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>3.31</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="X25" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3765,58 +3765,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
         <v>2.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AD26" t="n">
         <v>2.05</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.95</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="U27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.3</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AH27" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3.5</v>
       </c>
-      <c r="N28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.7</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="T28" t="n">
-        <v>2.35</v>
+        <v>3.02</v>
       </c>
       <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.53</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.81</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="M29" t="n">
-        <v>4.09</v>
+        <v>5.15</v>
       </c>
       <c r="N29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T29" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.05</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.49</v>
+        <v>1.52</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>6.57</v>
       </c>
       <c r="O30" t="n">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.59</v>
+        <v>3.18</v>
       </c>
       <c r="T30" t="n">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X30" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.44</v>
+        <v>2.98</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M31" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="N31" t="n">
         <v>1.5</v>
@@ -4422,7 +4422,7 @@
         <v>5.25</v>
       </c>
       <c r="P31" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q31" t="n">
         <v>1.9</v>
@@ -4431,7 +4431,7 @@
         <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="T31" t="n">
         <v>1.95</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>4.11</v>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.5</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>2.61</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="T32" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="U32" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
       </c>
       <c r="W32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.22</v>
       </c>
-      <c r="X32" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
+      <c r="AH32" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.79</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="M33" t="n">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>40.57</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>13.48</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="U33" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.39</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.41</v>
+        <v>1.46</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="AH33" t="n">
-        <v>10</v>
+        <v>1.79</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U34" t="n">
         <v>1.52</v>
       </c>
-      <c r="M34" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.36</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH34" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M35" t="n">
+        <v>13</v>
+      </c>
+      <c r="N35" t="n">
+        <v>46</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD35" t="n">
         <v>1.44</v>
       </c>
-      <c r="M35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>6</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.02</v>
       </c>
-      <c r="W35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH35" t="n">
-        <v>2.74</v>
+        <v>11.75</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="T37" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V37" t="n">
         <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X37" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
         <v>1.53</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
         <v>2.45</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.65</v>
-      </c>
       <c r="T38" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
         <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X38" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH38" t="n">
         <v>1.53</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45966.375</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.375</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1731,7 +1731,7 @@
         <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
         <v>1.6</v>
@@ -1740,7 +1740,7 @@
         <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Z10" t="n">
         <v>1.36</v>
@@ -1749,13 +1749,13 @@
         <v>5.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC10" t="n">
         <v>2.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
         <v>1.47</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45966.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
-        <v>3.02</v>
+        <v>7.75</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.98</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="X16" t="n">
-        <v>2.02</v>
+        <v>3.34</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA16" t="n">
         <v>3.2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>7.1</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.54</v>
+        <v>2.11</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>1.07</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="N17" t="n">
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>11.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA17" t="n">
         <v>3.5</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.95</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2742,34 +2742,34 @@
         <v>1.45</v>
       </c>
       <c r="O18" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
         <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y18" t="n">
         <v>2.35</v>
@@ -2781,13 +2781,13 @@
         <v>4.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
         <v>1.1</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.79</v>
+        <v>2.31</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,78 +2991,78 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>1.43</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.05</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.58</v>
-      </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,58 +3120,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="T21" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U21" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="Z21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA21" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
         <v>2</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>1.37</v>
       </c>
       <c r="O22" t="n">
-        <v>2.33</v>
+        <v>6.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.45</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>2.69</v>
+        <v>3.66</v>
       </c>
       <c r="T22" t="n">
-        <v>3.08</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.05</v>
+        <v>1.1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.63</v>
+        <v>1.76</v>
       </c>
       <c r="M23" t="n">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="N23" t="n">
-        <v>2.71</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>5.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.27</v>
+        <v>2.69</v>
       </c>
       <c r="T23" t="n">
-        <v>3.58</v>
+        <v>2.89</v>
       </c>
       <c r="U23" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>5</v>
+        <v>3.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.31</v>
+        <v>2.05</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="24">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>2.71</v>
       </c>
       <c r="O25" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.48</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X25" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Y25" t="n">
         <v>2.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.2</v>
+        <v>5.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,19 +3703,19 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y28" t="n">
         <v>2.3</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Z28" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.91</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="29">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
         <v>6</v>
@@ -4167,13 +4167,13 @@
         <v>2.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>6.61</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
@@ -4185,28 +4185,28 @@
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,77 +4281,77 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.52</v>
+        <v>3.14</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="N30" t="n">
-        <v>6.57</v>
+        <v>2.03</v>
       </c>
       <c r="O30" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X30" t="n">
         <v>6</v>
       </c>
-      <c r="R30" t="n">
+      <c r="Y30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.45</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.5</v>
+        <v>2.04</v>
       </c>
       <c r="M31" t="n">
-        <v>5.27</v>
+        <v>3.64</v>
       </c>
       <c r="N31" t="n">
-        <v>1.5</v>
+        <v>3.29</v>
       </c>
       <c r="O31" t="n">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>4.7</v>
+        <v>3.42</v>
       </c>
       <c r="T31" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="U31" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X31" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.49</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.86</v>
+        <v>2.49</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="M32" t="n">
-        <v>4.11</v>
+        <v>4.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.61</v>
+        <v>1.85</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S32" t="n">
-        <v>3.94</v>
+        <v>4.65</v>
       </c>
       <c r="T32" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="U32" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC32" t="n">
         <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
         <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.29</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O34" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
         <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="T34" t="n">
-        <v>2.52</v>
+        <v>3.02</v>
       </c>
       <c r="U34" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="X34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.72</v>
+        <v>3.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4926,28 +4926,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N35" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="O35" t="n">
         <v>1.22</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="Q35" t="n">
-        <v>13.48</v>
+        <v>21</v>
       </c>
       <c r="R35" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="T35" t="n">
         <v>1.71</v>
@@ -4959,22 +4959,22 @@
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.39</v>
+        <v>4.11</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="AC35" t="n">
         <v>2.63</v>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AH35" t="n">
         <v>11.75</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.75</v>
       </c>
     </row>
     <row r="38">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="N38" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
         <v>3.1</v>
@@ -5328,13 +5328,13 @@
         <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="T38" t="n">
         <v>3.2</v>
@@ -5346,19 +5346,19 @@
         <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X38" t="n">
         <v>2.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AB38" t="n">
         <v>1.2</v>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3.5</v>
       </c>
-      <c r="N39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>4.85</v>
-      </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="T39" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="U39" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="X39" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.24</v>
+        <v>4.33</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,78 +5571,78 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.2</v>
+        <v>3.67</v>
       </c>
       <c r="O40" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>4.14</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S40" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T40" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U40" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V40" t="n">
         <v>1.06</v>
       </c>
       <c r="W40" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI40" t="n">
         <v>0</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.19</v>
+        <v>2.93</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N41" t="n">
-        <v>3.38</v>
+        <v>2.24</v>
       </c>
       <c r="O41" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="P41" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.05</v>
+        <v>2.88</v>
       </c>
       <c r="R41" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S41" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T41" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.36</v>
       </c>
-      <c r="X41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.16</v>
+        <v>2.06</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.66</v>
+        <v>3.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T42" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U42" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V42" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W42" t="n">
         <v>1.4</v>
       </c>
       <c r="X42" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="Y42" t="n">
         <v>2.35</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB42" t="n">
         <v>1.18</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,6 +5908,135 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45966.33333333334</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45966.33333333334</v>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45966.33333333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45966.375</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45966.375</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45966.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45966.4375</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.79</v>
+        <v>2.31</v>
       </c>
       <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q17" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.9</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.45</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>6.1</v>
+        <v>1.79</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.15</v>
+        <v>11.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.88</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.6</v>
+        <v>4.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>3.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.75</v>
+        <v>7.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,77 +2991,77 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>7.9</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>6.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.98</v>
+        <v>2.15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="U20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.18</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3120,19 +3120,19 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="O21" t="n">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
         <v>2.05</v>
@@ -3144,31 +3144,31 @@
         <v>3.58</v>
       </c>
       <c r="T21" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
         <v>1.75</v>
@@ -3193,10 +3193,10 @@
         <v>1.13</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45966.61458333334</v>
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="M22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
         <v>1.37</v>
       </c>
       <c r="O22" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
         <v>3.66</v>
       </c>
       <c r="T22" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
         <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH22" t="n">
         <v>1.1</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45966.61458333334</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="M26" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="T26" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U26" t="n">
         <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.24</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45966.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.47</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.36</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.22</v>
       </c>
-      <c r="X27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45966.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="M28" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>3.08</v>
+        <v>2.51</v>
       </c>
       <c r="O28" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI28" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45966.69791666666</v>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M29" t="n">
         <v>5</v>
@@ -4164,49 +4164,49 @@
         <v>1.8</v>
       </c>
       <c r="P29" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.61</v>
+        <v>6.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.14</v>
+        <v>1.04</v>
       </c>
       <c r="M30" t="n">
-        <v>3.88</v>
+        <v>21</v>
       </c>
       <c r="N30" t="n">
-        <v>2.03</v>
+        <v>61</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
+        <v>22</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.63</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="AD30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.02</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X30" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.36</v>
+        <v>10</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>3.29</v>
+        <v>6.25</v>
       </c>
       <c r="O31" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="T31" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="U31" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="X31" t="n">
-        <v>4.4</v>
+        <v>3.74</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.49</v>
+        <v>2.98</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.75</v>
+        <v>2.64</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.9</v>
+        <v>2.11</v>
       </c>
       <c r="M32" t="n">
-        <v>4.8</v>
+        <v>3.73</v>
       </c>
       <c r="N32" t="n">
-        <v>1.52</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X32" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.21</v>
+        <v>2.34</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>3.37</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
         <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AB33" t="n">
         <v>1.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4797,31 +4797,31 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
         <v>2.59</v>
       </c>
       <c r="T34" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="U34" t="n">
         <v>1.33</v>
@@ -4830,19 +4830,19 @@
         <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X34" t="n">
         <v>3</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AB34" t="n">
         <v>1.25</v>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="M35" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="N35" t="n">
-        <v>29</v>
+        <v>1.4</v>
       </c>
       <c r="O35" t="n">
-        <v>1.22</v>
+        <v>5</v>
       </c>
       <c r="P35" t="n">
-        <v>3.72</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>1.85</v>
       </c>
       <c r="R35" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="T35" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="U35" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.11</v>
+        <v>3.49</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>2.63</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AH35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.53</v>
+        <v>3.05</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
-        <v>2.01</v>
+        <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.94</v>
+        <v>2.63</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="S36" t="n">
-        <v>3.18</v>
+        <v>3.94</v>
       </c>
       <c r="T36" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>3.8</v>
+        <v>6.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.94</v>
+        <v>2.82</v>
       </c>
       <c r="AA36" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="AB36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45966.70833333334</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.71</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.18</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45966.33333333334</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="O3" t="n">
-        <v>3.9</v>
+        <v>3.71</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.33</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AI3" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45966.33333333334</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>2.73</v>
       </c>
       <c r="M4" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6.82</v>
+        <v>2.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>2.58</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.1</v>
+        <v>1.72</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45966.33333333334</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45966.375</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45966.375</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.62</v>
@@ -1860,7 +1860,7 @@
         <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
         <v>1.6</v>
@@ -1878,7 +1878,7 @@
         <v>5.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
         <v>2.22</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AI11" t="n">
         <v>1.95</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2232,16 +2232,16 @@
         <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.4</v>
+        <v>5.77</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U14" t="n">
         <v>1.31</v>
@@ -2250,7 +2250,7 @@
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
         <v>2.86</v>
@@ -2262,7 +2262,7 @@
         <v>1.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AB14" t="n">
         <v>1.19</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.5</v>
       </c>
     </row>
     <row r="16">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>7.32</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="O16" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>6.7</v>
+        <v>1.48</v>
       </c>
       <c r="O17" t="n">
-        <v>2.31</v>
+        <v>7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.6</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.35</v>
+        <v>3.34</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.75</v>
+        <v>3.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.05</v>
+        <v>1.02</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.79</v>
+        <v>3.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.2</v>
+        <v>5.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="T18" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.35</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AH18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45966.60416666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="P19" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.98</v>
+        <v>10.21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="U19" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>2.02</v>
+        <v>2.97</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.21</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>3.45</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3000,34 +3000,34 @@
         <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
         <v>2.15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y20" t="n">
         <v>2.35</v>
@@ -3039,35 +3039,35 @@
         <v>4.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,86 +3120,86 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>1.46</v>
+        <v>6.7</v>
       </c>
       <c r="O21" t="n">
-        <v>6.25</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.05</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="S21" t="n">
-        <v>3.58</v>
+        <v>2.31</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>2.55</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH21" t="n">
         <v>2</v>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AI21" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
         <v>1.37</v>
@@ -3288,16 +3288,16 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
         <v>1.73</v>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>6.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.15</v>
+        <v>2.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>2.69</v>
+        <v>3.58</v>
       </c>
       <c r="T23" t="n">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA23" t="n">
-        <v>3.63</v>
+        <v>2.46</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>1.13</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="25">
@@ -3648,22 +3648,22 @@
         <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
         <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
         <v>3.58</v>
       </c>
       <c r="U25" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
         <v>1.12</v>
@@ -3684,13 +3684,13 @@
         <v>5.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC25" t="n">
         <v>2.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" t="n">
         <v>2.3</v>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,19 +3832,19 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="27">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="O27" t="n">
         <v>2.92</v>
@@ -3933,10 +3933,10 @@
         <v>2.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
         <v>4.13</v>
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.81</v>
+        <v>3.06</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
         <v>3.4</v>
@@ -4062,10 +4062,10 @@
         <v>3.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
         <v>3.31</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,86 +4152,86 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.8</v>
+        <v>3.65</v>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.1</v>
+        <v>2.73</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.74</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>3</v>
-      </c>
       <c r="AK29" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="30">
@@ -4284,10 +4284,10 @@
         <v>1.04</v>
       </c>
       <c r="M30" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="O30" t="n">
         <v>1.25</v>
@@ -4320,16 +4320,16 @@
         <v>8.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.39</v>
+        <v>4.11</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.41</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
         <v>2.63</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="N31" t="n">
-        <v>6.25</v>
+        <v>1.52</v>
       </c>
       <c r="O31" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>3.18</v>
+        <v>4.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.88</v>
       </c>
       <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
         <v>1.04</v>
       </c>
-      <c r="W31" t="n">
-        <v>1.26</v>
-      </c>
       <c r="X31" t="n">
-        <v>3.74</v>
+        <v>7.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>3.21</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>2.82</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>2.63</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.64</v>
+        <v>1.16</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.35</v>
+        <v>1.44</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="O32" t="n">
         <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U32" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,13 +4609,13 @@
         <v>1.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="T33" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V33" t="n">
         <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="X33" t="n">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4738,13 +4738,13 @@
         <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.18</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>3</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R35" t="n">
         <v>1.4</v>
       </c>
-      <c r="O35" t="n">
-        <v>5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.2</v>
-      </c>
       <c r="S35" t="n">
-        <v>4.9</v>
+        <v>2.59</v>
       </c>
       <c r="T35" t="n">
-        <v>1.88</v>
+        <v>2.95</v>
       </c>
       <c r="U35" t="n">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="X35" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.49</v>
+        <v>1.77</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.88</v>
+        <v>3.54</v>
       </c>
       <c r="AB35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>3.29</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T36" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.05</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X36" t="n">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.12</v>
+        <v>2.49</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,19 +5251,19 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.75</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="38">
@@ -5325,31 +5325,31 @@
         <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
         <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S38" t="n">
         <v>2.66</v>
       </c>
       <c r="T38" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="U38" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X38" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="Y38" t="n">
         <v>2.13</v>
@@ -5358,16 +5358,16 @@
         <v>1.63</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB38" t="n">
         <v>1.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5451,31 +5451,31 @@
         <v>2.75</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="P39" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
         <v>2.64</v>
       </c>
       <c r="T39" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W39" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X39" t="n">
         <v>2.75</v>
@@ -5487,7 +5487,7 @@
         <v>1.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB39" t="n">
         <v>1.2</v>
@@ -5583,31 +5583,31 @@
         <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
         <v>2.69</v>
       </c>
       <c r="T40" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V40" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X40" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="Y40" t="n">
         <v>1.92</v>
@@ -5616,16 +5616,16 @@
         <v>1.78</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="AB40" t="n">
         <v>1.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
         <v>1.85</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,43 +5700,43 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.93</v>
+        <v>2.06</v>
       </c>
       <c r="M41" t="n">
         <v>3.02</v>
       </c>
       <c r="N41" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3.6</v>
+        <v>2.81</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.88</v>
+        <v>4.37</v>
       </c>
       <c r="R41" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T41" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Y41" t="n">
         <v>2.35</v>
@@ -5745,16 +5745,16 @@
         <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,43 +5829,43 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.06</v>
+        <v>2.93</v>
       </c>
       <c r="M42" t="n">
         <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P42" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.9</v>
+        <v>3.01</v>
       </c>
       <c r="R42" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T42" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U42" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X42" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="Y42" t="n">
         <v>2.35</v>
@@ -5874,16 +5874,16 @@
         <v>1.6</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5967,31 +5967,31 @@
         <v>1.84</v>
       </c>
       <c r="O43" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P43" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q43" t="n">
         <v>2.63</v>
       </c>
       <c r="R43" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
         <v>2.42</v>
       </c>
       <c r="T43" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V43" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W43" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X43" t="n">
         <v>2.63</v>
@@ -6009,10 +6009,10 @@
         <v>1.18</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>2.79</v>
       </c>
       <c r="M2" t="n">
-        <v>4.4</v>
+        <v>3.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>2.43</v>
       </c>
       <c r="O2" t="n">
-        <v>1.95</v>
+        <v>3.57</v>
       </c>
       <c r="P2" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.5</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45966.33333333334</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.79</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
-        <v>2.43</v>
+        <v>6.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.71</v>
+        <v>1.95</v>
       </c>
       <c r="P3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AA3" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45966.33333333334</v>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
         <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="P4" t="n">
         <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
@@ -951,31 +951,31 @@
         <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
         <v>1.22</v>
       </c>
       <c r="X4" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
         <v>1.64</v>
@@ -997,7 +997,7 @@
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" t="n">
         <v>2.3</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45966.375</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45966.375</v>
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>2.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA9" t="n">
         <v>4.55</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,58 +1704,58 @@
         <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
         <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45966.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N11" t="n">
         <v>2.9</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Y11" t="n">
         <v>3.25</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI11" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y11" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45966.4375</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI12" t="n">
         <v>3.1</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45966.4375</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45966.4375</v>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
         <v>4.9</v>
@@ -2232,7 +2232,7 @@
         <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.77</v>
+        <v>5.4</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
@@ -2241,7 +2241,7 @@
         <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
         <v>1.31</v>
@@ -2250,22 +2250,22 @@
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
         <v>2.86</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA14" t="n">
         <v>3.78</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AC14" t="n">
         <v>2.14</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7.32</v>
+        <v>14</v>
       </c>
       <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O16" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI16" t="n">
         <v>4.5</v>
       </c>
-      <c r="N16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="O16" t="n">
-        <v>8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45966.54166666666</v>
@@ -2604,19 +2604,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>7.55</v>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
         <v>1.85</v>
@@ -2625,34 +2625,34 @@
         <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="T17" t="n">
         <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
       </c>
       <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.28</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.44</v>
       </c>
       <c r="AC17" t="n">
         <v>2.11</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
         <v>1.02</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3.13</v>
+        <v>1.89</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.2</v>
+        <v>8.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.7</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AA18" t="n">
-        <v>6.27</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.68</v>
+        <v>3.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45966.60416666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.27</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N19" t="n">
-        <v>12</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="X19" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.05</v>
+        <v>2.49</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.24</v>
+        <v>3.9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>5.25</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45966.60416666666</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,58 +2991,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.9</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.45</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>7.3</v>
+        <v>2.33</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.49</v>
       </c>
-      <c r="S20" t="n">
+      <c r="X20" t="n">
         <v>2.31</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.43</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AA20" t="n">
-        <v>4.88</v>
+        <v>5.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
         <v>1.53</v>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.43</v>
+        <v>3.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="N21" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>2.97</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>5.26</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="S21" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="T21" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="X21" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.7</v>
+        <v>6.27</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="N22" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="P22" t="n">
         <v>2.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
@@ -3285,19 +3285,19 @@
         <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
         <v>1.73</v>
@@ -3378,28 +3378,28 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O23" t="n">
         <v>6</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O23" t="n">
-        <v>6.25</v>
-      </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
         <v>2.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
         <v>2.45</v>
@@ -3417,22 +3417,22 @@
         <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AA23" t="n">
         <v>2.46</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC23" t="n">
         <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AI23" t="n">
         <v>3</v>
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,86 +3507,86 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.76</v>
+        <v>2.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.38</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="T24" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.4</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,19 +3832,19 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>3.08</v>
+        <v>2.15</v>
       </c>
       <c r="O27" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>2.81</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="X27" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.13</v>
+        <v>3.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3964,13 +3964,13 @@
         <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45966.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.06</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.32</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X28" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.31</v>
+        <v>4.13</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45966.69791666666</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.25</v>
+        <v>1.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>16</v>
       </c>
       <c r="N29" t="n">
-        <v>2.1</v>
+        <v>45</v>
       </c>
       <c r="O29" t="n">
-        <v>3.65</v>
+        <v>1.22</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.73</v>
+        <v>19</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="S29" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.73</v>
+        <v>1.77</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.98</v>
+        <v>3.39</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.02</v>
+        <v>1.57</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,19 +4219,19 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.32</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.23</v>
+        <v>1.08</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3.94</v>
       </c>
       <c r="T30" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="U30" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.11</v>
+        <v>2.75</v>
       </c>
       <c r="AA30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI30" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>7</v>
+        <v>1.72</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.9</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="N31" t="n">
-        <v>1.52</v>
+        <v>6.5</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.85</v>
+        <v>6.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.21</v>
+        <v>2.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>2.63</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.16</v>
+        <v>2.9</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>5.8</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.37</v>
+        <v>1.41</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="T32" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.04</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.21</v>
-      </c>
       <c r="X32" t="n">
-        <v>4.25</v>
+        <v>7.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>3.49</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="M33" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>5.8</v>
+        <v>2.83</v>
       </c>
       <c r="O33" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>3.63</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="T33" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W33" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="X33" t="n">
-        <v>3.74</v>
+        <v>3.21</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.98</v>
+        <v>3.52</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.64</v>
+        <v>1.56</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.42</v>
       </c>
-      <c r="M34" t="n">
-        <v>5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.97</v>
+        <v>1.85</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="N35" t="n">
-        <v>3.1</v>
+        <v>6.75</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="P35" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.66</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.4</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="N36" t="n">
-        <v>3.29</v>
+        <v>2.85</v>
       </c>
       <c r="O36" t="n">
         <v>2.5</v>
@@ -5070,7 +5070,7 @@
         <v>2.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="R36" t="n">
         <v>1.29</v>
@@ -5082,7 +5082,7 @@
         <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -5094,22 +5094,22 @@
         <v>4.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
         <v>2.49</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AI36" t="n">
         <v>1.72</v>
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.14</v>
+        <v>2.61</v>
       </c>
       <c r="M37" t="n">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
         <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.23</v>
+        <v>1.48</v>
       </c>
       <c r="S37" t="n">
-        <v>3.94</v>
+        <v>2.53</v>
       </c>
       <c r="T37" t="n">
-        <v>2.05</v>
+        <v>3.36</v>
       </c>
       <c r="U37" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="X37" t="n">
-        <v>6.25</v>
+        <v>2.71</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>2.27</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>4.34</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,19 +5251,19 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI37" t="n">
         <v>2.05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="38">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>4.8</v>
       </c>
       <c r="O38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA38" t="n">
         <v>3.1</v>
       </c>
-      <c r="P38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AB38" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45966.79166666666</v>
@@ -5442,28 +5442,28 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="M39" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="O39" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
         <v>2.07</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
         <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="T39" t="n">
         <v>3.22</v>
@@ -5481,10 +5481,10 @@
         <v>2.75</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA39" t="n">
         <v>4.2</v>
@@ -5512,13 +5512,13 @@
         <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45966.79166666666</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N40" t="n">
-        <v>3.67</v>
+        <v>4.48</v>
       </c>
       <c r="O40" t="n">
         <v>2.4</v>
@@ -5610,22 +5610,22 @@
         <v>3.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5644,10 +5644,10 @@
         <v>1.85</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45966.8125</v>
@@ -5700,16 +5700,16 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O41" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
         <v>1.99</v>
@@ -5721,13 +5721,13 @@
         <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T41" t="n">
         <v>3.1</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
         <v>1.03</v>
@@ -5739,7 +5739,7 @@
         <v>2.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Z41" t="n">
         <v>1.6</v>
@@ -5773,10 +5773,10 @@
         <v>1.65</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45966.83333333334</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="N42" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="O42" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P42" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="R42" t="n">
         <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="T42" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U42" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.37</v>
       </c>
-      <c r="X42" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45966.83333333334</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.77</v>
+        <v>4.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
         <v>4.8</v>
@@ -5976,7 +5976,7 @@
         <v>2.63</v>
       </c>
       <c r="R43" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S43" t="n">
         <v>2.42</v>
@@ -5997,10 +5997,10 @@
         <v>2.63</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA43" t="n">
         <v>4.5</v>
@@ -6009,10 +6009,10 @@
         <v>1.18</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH43" t="n">
         <v>1.25</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45966.89583333334</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.79</v>
+        <v>3.25</v>
       </c>
       <c r="M2" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="O2" t="n">
-        <v>3.57</v>
+        <v>3.87</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="U2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.27</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AI2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45966.33333333334</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>2.79</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="N3" t="n">
-        <v>6.5</v>
+        <v>2.43</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>3.57</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>3.12</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45966.33333333334</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2.06</v>
+        <v>6.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.87</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.72</v>
+        <v>3.1</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45966.33333333334</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45966.375</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.56</v>
+        <v>4.68</v>
       </c>
       <c r="R10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AB10" t="n">
         <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" t="n">
         <v>1.9</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.56</v>
+        <v>3.14</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>4.15</v>
+        <v>3.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
         <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.15</v>
+        <v>5.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45966.4375</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="O12" t="n">
-        <v>6.04</v>
+        <v>5.77</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.49</v>
@@ -1983,37 +1983,37 @@
         <v>2.34</v>
       </c>
       <c r="T12" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
         <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AI12" t="n">
         <v>3.1</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.3</v>
       </c>
       <c r="R13" t="n">
         <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45966.4375</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N16" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
         <v>11.4</v>
@@ -2499,37 +2499,37 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
         <v>1.04</v>
@@ -2733,58 +2733,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="N18" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P18" t="n">
         <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.1</v>
+        <v>11.2</v>
       </c>
       <c r="R18" t="n">
         <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
         <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AD18" t="n">
         <v>1.44</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AI18" t="n">
         <v>1.24</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,58 +2862,58 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q19" t="n">
         <v>6</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="R19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.53</v>
       </c>
-      <c r="O19" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X19" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
         <v>1.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
         <v>1.53</v>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>2.49</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.43</v>
+        <v>3.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45966.60416666666</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.33</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="S20" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="W20" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="X20" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.62</v>
+        <v>3.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.1</v>
+        <v>6.27</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.03</v>
+        <v>7.9</v>
       </c>
       <c r="M21" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="O21" t="n">
-        <v>2.97</v>
+        <v>7.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.26</v>
+        <v>2.31</v>
       </c>
       <c r="R21" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="V21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.1</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AI21" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="O22" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="U22" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45966.61458333334</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.86</v>
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="N23" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="T23" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AI23" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45966.61458333334</v>
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="P26" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
         <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="Z26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.83</v>
       </c>
-      <c r="AA26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45966.69791666666</v>
@@ -3897,58 +3897,58 @@
         <v>3.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
         <v>3.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AI27" t="n">
         <v>2.23</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="P28" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="T28" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.13</v>
+        <v>3.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45966.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.05</v>
+        <v>3.4</v>
       </c>
       <c r="M29" t="n">
-        <v>16</v>
+        <v>4.01</v>
       </c>
       <c r="N29" t="n">
-        <v>45</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
-        <v>1.22</v>
+        <v>3.22</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>2.51</v>
       </c>
       <c r="R29" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>8.5</v>
+        <v>5.35</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.39</v>
+        <v>2.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.08</v>
+        <v>2.05</v>
       </c>
       <c r="AJ29" t="n">
-        <v>7</v>
+        <v>1.72</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.1</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.1</v>
+        <v>6.9</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="T30" t="n">
         <v>2.05</v>
       </c>
       <c r="U30" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA30" t="n">
         <v>2.11</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>2.07</v>
       </c>
       <c r="M31" t="n">
-        <v>5.4</v>
+        <v>3.74</v>
       </c>
       <c r="N31" t="n">
-        <v>6.5</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.1</v>
+        <v>3.69</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.14</v>
+        <v>2.51</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="N32" t="n">
-        <v>1.41</v>
+        <v>41</v>
       </c>
       <c r="O32" t="n">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="P32" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.85</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S32" t="n">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
         <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.49</v>
+        <v>3.39</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.15</v>
+        <v>10.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.75</v>
+        <v>1.08</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.44</v>
+        <v>7</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.38</v>
+        <v>6.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>5.35</v>
       </c>
       <c r="N33" t="n">
-        <v>2.83</v>
+        <v>1.42</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.63</v>
+        <v>1.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="S33" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>2.81</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,62 +4797,62 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.9</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="M35" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>6.75</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="T35" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U35" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X35" t="n">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.98</v>
+        <v>2.68</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.77</v>
+        <v>1.96</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.35</v>
+        <v>2.25</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>1.32</v>
       </c>
       <c r="M36" t="n">
-        <v>3.73</v>
+        <v>4.74</v>
       </c>
       <c r="N36" t="n">
-        <v>2.85</v>
+        <v>7.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="P36" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.69</v>
+        <v>6.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S36" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U36" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.49</v>
+        <v>2.93</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.75</v>
+        <v>2.98</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.61</v>
+        <v>1.73</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.53</v>
+        <v>3.11</v>
       </c>
       <c r="T37" t="n">
-        <v>3.36</v>
+        <v>2.69</v>
       </c>
       <c r="U37" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="V37" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.34</v>
+        <v>3.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.41</v>
+        <v>2.05</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45966.79166666666</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.51</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S38" t="n">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="T38" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U38" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X38" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z38" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI38" t="n">
         <v>2.05</v>
       </c>
-      <c r="AI38" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ38" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45966.79166666666</v>
@@ -5442,52 +5442,52 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
         <v>2.95</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="P39" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="R39" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T39" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U39" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X39" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB39" t="n">
         <v>1.2</v>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AI39" t="n">
         <v>1.95</v>
@@ -5571,34 +5571,34 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>4.48</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
         <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
         <v>2.69</v>
       </c>
       <c r="T40" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U40" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
@@ -5607,25 +5607,25 @@
         <v>1.3</v>
       </c>
       <c r="X40" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
         <v>1.85</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P41" t="n">
         <v>2.1</v>
       </c>
-      <c r="M41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.99</v>
-      </c>
       <c r="Q41" t="n">
-        <v>4.37</v>
+        <v>2.88</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S41" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="T41" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.37</v>
       </c>
-      <c r="X41" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AI41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45966.83333333334</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T42" t="n">
         <v>3.15</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.99</v>
-      </c>
       <c r="U42" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W42" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="X42" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI42" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ42" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45966.83333333334</v>
@@ -5964,19 +5964,19 @@
         <v>3.25</v>
       </c>
       <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P43" t="n">
         <v>1.95</v>
-      </c>
-      <c r="O43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.08</v>
       </c>
       <c r="Q43" t="n">
         <v>2.63</v>
       </c>
       <c r="R43" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
         <v>2.42</v>
@@ -5988,10 +5988,10 @@
         <v>1.32</v>
       </c>
       <c r="V43" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X43" t="n">
         <v>2.63</v>
@@ -6009,7 +6009,7 @@
         <v>1.18</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AD43" t="n">
         <v>1.75</v>
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="AH43" t="n">
         <v>1.25</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="M2" t="n">
         <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="O2" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.63</v>
       </c>
       <c r="U2" t="n">
         <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
         <v>2.3</v>
@@ -807,10 +807,10 @@
         <v>2.43</v>
       </c>
       <c r="O3" t="n">
-        <v>3.57</v>
+        <v>3.73</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
         <v>3.12</v>
@@ -819,7 +819,7 @@
         <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
         <v>3.2</v>
@@ -837,7 +837,7 @@
         <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Z3" t="n">
         <v>1.58</v>
@@ -930,10 +930,10 @@
         <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.95</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45966.375</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45966.375</v>
@@ -1452,53 +1452,53 @@
         <v>1.82</v>
       </c>
       <c r="O8" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y9" t="n">
         <v>2.49</v>
       </c>
-      <c r="Y9" t="n">
-        <v>2.39</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AI9" t="n">
         <v>1.76</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.68</v>
+        <v>2.31</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.85</v>
+        <v>5.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>2.71</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45966.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="P11" t="n">
         <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="T11" t="n">
-        <v>3.82</v>
+        <v>4.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI11" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y11" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45966.4375</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>1.98</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>5.77</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>2.34</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
-        <v>3.34</v>
+        <v>3.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="X12" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.61</v>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AI12" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45966.4375</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.63</v>
+        <v>2.57</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.04</v>
+        <v>2.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.15</v>
+        <v>5.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45966.4375</v>
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
         <v>4.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.4</v>
+        <v>5.95</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
@@ -2250,22 +2250,22 @@
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
         <v>2.86</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AC14" t="n">
         <v>2.14</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.7</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.24</v>
       </c>
-      <c r="O16" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="X16" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45966.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="O17" t="n">
-        <v>7.55</v>
+        <v>11.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Y17" t="n">
         <v>1.86</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45966.54166666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>7.9</v>
       </c>
       <c r="M18" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>1.45</v>
       </c>
       <c r="O18" t="n">
-        <v>1.8</v>
+        <v>8.51</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.2</v>
+        <v>2.35</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="T18" t="n">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="X18" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.24</v>
+        <v>3.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5.25</v>
+        <v>1.43</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45966.60416666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="S19" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="T19" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="U19" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>3.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.1</v>
+        <v>6.27</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45966.60416666666</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="P20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AA20" t="n">
-        <v>6.27</v>
+        <v>3.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>3.24</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,62 +3120,62 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.45</v>
       </c>
-      <c r="O21" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.1</v>
+        <v>1.98</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.43</v>
+        <v>3.2</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3252,58 +3252,58 @@
         <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.28</v>
+        <v>2.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45966.61458333334</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,58 +3378,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="U23" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AD23" t="n">
         <v>2</v>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI23" t="n">
         <v>3</v>
       </c>
-      <c r="AH23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45966.61458333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.98</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>1.84</v>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.5</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.32</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>4.6</v>
+        <v>3.11</v>
       </c>
       <c r="N25" t="n">
-        <v>9.199999999999999</v>
+        <v>2.71</v>
       </c>
       <c r="O25" t="n">
-        <v>1.82</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q25" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="R25" t="n">
+      <c r="Y25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.38</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>3</v>
-      </c>
       <c r="AI25" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45966.66666666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>3.06</v>
       </c>
       <c r="M26" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3.1</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.74</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.3</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45966.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="O27" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.82</v>
+        <v>4.28</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="T27" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.3</v>
       </c>
-      <c r="X27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45966.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,62 +4023,62 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.75</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.77</v>
       </c>
       <c r="U28" t="n">
         <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X28" t="n">
         <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.27</v>
       </c>
-      <c r="AH28" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AI28" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45966.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="M29" t="n">
-        <v>4.01</v>
+        <v>14</v>
       </c>
       <c r="N29" t="n">
+        <v>29</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>23</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U29" t="n">
         <v>2.05</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.76</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>5.35</v>
+        <v>8.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.75</v>
+        <v>4.11</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.8</v>
+        <v>1.46</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.05</v>
+        <v>1.08</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N30" t="n">
-        <v>6.9</v>
+        <v>1.52</v>
       </c>
       <c r="O30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AA30" t="n">
         <v>1.8</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X30" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="Y30" t="n">
+      <c r="AB30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.44</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.69</v>
+        <v>3.19</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>3.36</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="Z31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="M32" t="n">
-        <v>16</v>
+        <v>3.64</v>
       </c>
       <c r="N32" t="n">
-        <v>41</v>
+        <v>3.29</v>
       </c>
       <c r="O32" t="n">
-        <v>1.25</v>
+        <v>2.65</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>2.26</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.77</v>
+        <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.39</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.53</v>
+        <v>2.46</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AH32" t="n">
-        <v>10.5</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.08</v>
+        <v>1.72</v>
       </c>
       <c r="AJ32" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.2</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>1.42</v>
+        <v>5.8</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="P33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH33" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X33" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AI33" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.44</v>
+        <v>3.35</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P34" t="n">
         <v>2.5</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="AB34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.36</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI34" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4926,58 +4926,58 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>3.37</v>
       </c>
       <c r="O35" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="U35" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
         <v>2.39</v>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AI35" t="n">
         <v>1.66</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="M36" t="n">
-        <v>4.74</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="P36" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>3.24</v>
+        <v>4.05</v>
       </c>
       <c r="T36" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="U36" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.93</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.98</v>
+        <v>2.52</v>
       </c>
       <c r="AI36" t="n">
         <v>1.4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>4.7</v>
+        <v>2.75</v>
       </c>
       <c r="O37" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S37" t="n">
-        <v>3.11</v>
+        <v>2.53</v>
       </c>
       <c r="T37" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="U37" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="X37" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="Z37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC37" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD37" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI37" t="n">
         <v>2.05</v>
       </c>
-      <c r="AI37" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45966.79166666666</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>2.6</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45966.79166666666</v>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK43"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.73</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N2" t="n">
-        <v>2.33</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.85</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.57</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.72</v>
+        <v>3.1</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45966.33333333334</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="M3" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>3.73</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.12</v>
+        <v>2.57</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>2.83</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.05</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45966.33333333334</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>2.79</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.2</v>
+        <v>2.43</v>
       </c>
       <c r="O4" t="n">
-        <v>1.95</v>
+        <v>3.73</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>3.12</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45966.33333333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.37</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.07</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.79</v>
+        <v>2.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45966.375</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.47</v>
+        <v>1.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45966.375</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="O9" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
         <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AI9" t="n">
         <v>1.76</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>4.7</v>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>6.5</v>
+        <v>11.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.36</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA16" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.09</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45966.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,87 +2600,87 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.24</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>11.4</v>
+        <v>2.64</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>3.65</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Z17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45966.54166666666</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="N18" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O18" t="n">
-        <v>8.51</v>
+        <v>6.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.11</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="X18" t="n">
-        <v>1.91</v>
+        <v>3.65</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>2.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.11</v>
+        <v>2.09</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,19 +2800,19 @@
         </is>
       </c>
       <c r="AG18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AK18" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,86 +2862,86 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y19" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="Z19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>4.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AK19" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="P20" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.75</v>
+        <v>5.03</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.8</v>
+        <v>5.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.24</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AJ20" t="n">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="N21" t="n">
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="O21" t="n">
-        <v>2.34</v>
+        <v>1.77</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.03</v>
+        <v>10.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="U21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.25</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.98</v>
+        <v>3.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45966.60416666666</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q22" t="n">
         <v>5.1</v>
       </c>
-      <c r="N22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="O22" t="n">
-        <v>7</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.75</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>2.08</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="U22" t="n">
-        <v>1.65</v>
+        <v>1.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>2.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.47</v>
+        <v>3.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.57</v>
+        <v>1.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>6.27</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>1.09</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,19 +3316,19 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.35</v>
+        <v>2.7</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="M23" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>8.51</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>2.11</v>
       </c>
       <c r="T23" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>1.91</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.57</v>
+        <v>8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.86</v>
+        <v>3.11</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>2.77</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AI23" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6.9</v>
+        <v>1.47</v>
       </c>
       <c r="O24" t="n">
-        <v>1.84</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.6</v>
+        <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2</v>
       </c>
-      <c r="Z24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.14</v>
+        <v>2.77</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.1</v>
+        <v>1.12</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.11</v>
+        <v>5.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.71</v>
+        <v>1.37</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.31</v>
+        <v>3.85</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="U25" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="V25" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>5.37</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.15</v>
+        <v>1.63</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,19 +3703,19 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.06</v>
+        <v>1.76</v>
       </c>
       <c r="M26" t="n">
         <v>3.28</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>3.52</v>
+        <v>2.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
         <v>3.1</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
         <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,19 +3832,19 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,86 +3894,86 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="M27" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3.08</v>
+        <v>2.71</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.28</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>2.72</v>
+        <v>2.31</v>
       </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W27" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X27" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="Y27" t="n">
         <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.15</v>
+        <v>5.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AC27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>2</v>
       </c>
-      <c r="AD27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AK27" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="M28" t="n">
-        <v>3.47</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.8</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X28" t="n">
         <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45966.69791666666</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,86 +4152,86 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.04</v>
       </c>
-      <c r="M29" t="n">
-        <v>14</v>
-      </c>
-      <c r="N29" t="n">
-        <v>29</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>23</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S29" t="n">
-        <v>5</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="W29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.62</v>
       </c>
-      <c r="U29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>10</v>
-      </c>
       <c r="AI29" t="n">
-        <v>1.08</v>
+        <v>1.83</v>
       </c>
       <c r="AJ29" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="M30" t="n">
-        <v>4.8</v>
+        <v>3.47</v>
       </c>
       <c r="N30" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="X30" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.21</v>
+        <v>1.98</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.94</v>
+        <v>1.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.99</v>
+        <v>1.95</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,19 +4348,19 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="31">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.29</v>
+        <v>5.8</v>
       </c>
       <c r="O32" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="P32" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="T32" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="U32" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X32" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="M33" t="n">
+        <v>14</v>
+      </c>
+      <c r="N33" t="n">
+        <v>29</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P33" t="n">
         <v>4.1</v>
       </c>
-      <c r="N33" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.24</v>
-      </c>
       <c r="Q33" t="n">
+        <v>23</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>7</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>3.35</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,28 +4797,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.14</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>3.01</v>
+        <v>1.73</v>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.54</v>
+        <v>5.25</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="T34" t="n">
         <v>2.05</v>
@@ -4830,50 +4830,50 @@
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
         <v>6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AC34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,28 +5055,28 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.42</v>
+        <v>3.14</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>2.03</v>
       </c>
       <c r="O36" t="n">
-        <v>1.73</v>
+        <v>3.01</v>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.25</v>
+        <v>2.54</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S36" t="n">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="T36" t="n">
         <v>2.05</v>
@@ -5088,28 +5088,28 @@
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X36" t="n">
         <v>6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.52</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45966.70833333334</v>
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,86 +5184,86 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="N37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI37" t="n">
         <v>2.75</v>
       </c>
-      <c r="O37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AK37" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>3.29</v>
       </c>
       <c r="O38" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="P38" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.3</v>
+        <v>3.62</v>
       </c>
       <c r="R38" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S38" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.69</v>
+        <v>2.42</v>
       </c>
       <c r="U38" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X38" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,19 +5380,19 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
+        <v>4</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA39" t="n">
         <v>3.1</v>
       </c>
-      <c r="N39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,19 +5509,19 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.1</v>
+        <v>3.16</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="O40" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="T40" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="U40" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W40" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X40" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.49</v>
+        <v>4.35</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5641,16 +5641,16 @@
         <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O41" t="n">
         <v>3.25</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="R41" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T41" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W41" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,19 +5767,19 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,86 +5829,86 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P42" t="n">
         <v>2.15</v>
       </c>
-      <c r="M42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.99</v>
-      </c>
       <c r="Q42" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S42" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="T42" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="U42" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="V42" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W42" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="X42" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD42" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AI42" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45966.83333333334</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="43">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="O43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Q43" t="n">
-        <v>2.63</v>
+        <v>3.82</v>
       </c>
       <c r="R43" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S43" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="T43" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="U43" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V43" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W43" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="X43" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="Y43" t="n">
         <v>2.35</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC43" t="n">
         <v>1.95</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,18 +6025,276 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK43" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK44" s="3" t="n">
+        <v>45966.83333333334</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AH45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI45" t="n">
         <v>2.66</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AJ45" t="n">
         <v>1.72</v>
       </c>
-      <c r="AK43" s="3" t="n">
+      <c r="AK45" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:Z45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,115 +508,60 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>homeGoals</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -678,20 +623,20 @@
         <v>6.2</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S2" t="n">
         <v>1.95</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -705,49 +650,12 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ2" t="n">
         <v>3.1</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="Z2" s="3" t="n">
         <v>45966.33333333334</v>
       </c>
     </row>
@@ -807,76 +715,39 @@
         <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.57</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="S3" t="n">
-        <v>2.83</v>
+        <v>1.89</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ3" t="n">
         <v>1.72</v>
       </c>
-      <c r="AK3" s="3" t="n">
+      <c r="Z3" s="3" t="n">
         <v>45966.33333333334</v>
       </c>
     </row>
@@ -936,76 +807,39 @@
         <v>2.43</v>
       </c>
       <c r="O4" t="n">
-        <v>3.73</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.12</v>
+        <v>1.27</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ4" t="n">
         <v>2</v>
       </c>
-      <c r="AK4" s="3" t="n">
+      <c r="Z4" s="3" t="n">
         <v>45966.33333333334</v>
       </c>
     </row>
@@ -1065,19 +899,19 @@
         <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1089,52 +923,15 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AJ5" t="n">
         <v>3</v>
       </c>
-      <c r="AK5" s="3" t="n">
+      <c r="Z5" s="3" t="n">
         <v>45966.375</v>
       </c>
     </row>
@@ -1194,76 +991,39 @@
         <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.47</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>1.41</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="S6" t="n">
-        <v>2.79</v>
+        <v>2.01</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="X6" t="n">
-        <v>3.75</v>
+        <v>1.77</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ6" t="n">
         <v>2.35</v>
       </c>
-      <c r="AK6" s="3" t="n">
+      <c r="Z6" s="3" t="n">
         <v>45966.375</v>
       </c>
     </row>
@@ -1355,44 +1115,7 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="3" t="n">
+      <c r="Z7" s="3" t="n">
         <v>45966.375</v>
       </c>
     </row>
@@ -1452,76 +1175,39 @@
         <v>1.82</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="W8" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>45966.39583333334</v>
       </c>
     </row>
@@ -1581,76 +1267,39 @@
         <v>2.99</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.05</v>
+        <v>1.29</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AJ9" t="n">
         <v>2.47</v>
       </c>
-      <c r="AK9" s="3" t="n">
+      <c r="Z9" s="3" t="n">
         <v>45966.41666666666</v>
       </c>
     </row>
@@ -1710,76 +1359,39 @@
         <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>1.62</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>3.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.31</v>
+        <v>1.21</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.19</v>
+        <v>1.55</v>
       </c>
       <c r="T10" t="n">
-        <v>3.58</v>
+        <v>2.71</v>
       </c>
       <c r="U10" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AJ10" t="n">
         <v>1.53</v>
       </c>
-      <c r="AK10" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>45966.4375</v>
       </c>
     </row>
@@ -1839,76 +1451,39 @@
         <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>4.3</v>
+        <v>1.68</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>4.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.05</v>
+        <v>1.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.68</v>
+        <v>3.04</v>
       </c>
       <c r="S11" t="n">
-        <v>2.11</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>4.05</v>
+        <v>2.51</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ11" t="n">
         <v>2.25</v>
       </c>
-      <c r="AK11" s="3" t="n">
+      <c r="Z11" s="3" t="n">
         <v>45966.4375</v>
       </c>
     </row>
@@ -1968,76 +1543,39 @@
         <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82</v>
+        <v>3.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.2</v>
+        <v>1.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>2.81</v>
       </c>
       <c r="S12" t="n">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.86</v>
+        <v>2.43</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X12" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ12" t="n">
         <v>2.45</v>
       </c>
-      <c r="AK12" s="3" t="n">
+      <c r="Z12" s="3" t="n">
         <v>45966.4375</v>
       </c>
     </row>
@@ -2097,76 +1635,39 @@
         <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.57</v>
+        <v>1.56</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>3.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>1.52</v>
       </c>
       <c r="T13" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="X13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y13" t="n">
         <v>2.37</v>
       </c>
-      <c r="Y13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AK13" s="3" t="n">
+      <c r="Z13" s="3" t="n">
         <v>45966.4375</v>
       </c>
     </row>
@@ -2226,76 +1727,39 @@
         <v>4.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.95</v>
+        <v>1.31</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>2.33</v>
       </c>
       <c r="X14" t="n">
-        <v>2.86</v>
+        <v>1.57</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ14" t="n">
         <v>2.94</v>
       </c>
-      <c r="AK14" s="3" t="n">
+      <c r="Z14" s="3" t="n">
         <v>45966.45833333334</v>
       </c>
     </row>
@@ -2387,44 +1851,7 @@
       <c r="Y15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
+      <c r="Z15" s="3" t="n">
         <v>45966.5</v>
       </c>
     </row>
@@ -2484,76 +1911,39 @@
         <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>11.4</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB16" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK16" s="3" t="n">
+      <c r="Z16" s="3" t="n">
         <v>45966.54166666666</v>
       </c>
     </row>
@@ -2613,76 +2003,39 @@
         <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.64</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.65</v>
+        <v>1.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="S17" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="T17" t="n">
-        <v>2.43</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AK17" s="3" t="n">
+      <c r="Z17" s="3" t="n">
         <v>45966.54166666666</v>
       </c>
     </row>
@@ -2742,76 +2095,39 @@
         <v>1.48</v>
       </c>
       <c r="O18" t="n">
-        <v>6.5</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="R18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.36</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK18" s="3" t="n">
+      <c r="Z18" s="3" t="n">
         <v>45966.54166666666</v>
       </c>
     </row>
@@ -2871,76 +2187,39 @@
         <v>6.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.84</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.6</v>
+        <v>1.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ19" t="n">
         <v>4.2</v>
       </c>
-      <c r="AK19" s="3" t="n">
+      <c r="Z19" s="3" t="n">
         <v>45966.58333333334</v>
       </c>
     </row>
@@ -3000,76 +2279,39 @@
         <v>6.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.34</v>
+        <v>1.61</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.03</v>
+        <v>1.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="T20" t="n">
-        <v>3.58</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="X20" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ20" t="n">
         <v>3.2</v>
       </c>
-      <c r="AK20" s="3" t="n">
+      <c r="Z20" s="3" t="n">
         <v>45966.60416666666</v>
       </c>
     </row>
@@ -3129,76 +2371,39 @@
         <v>12</v>
       </c>
       <c r="O21" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>2.13</v>
+        <v>3.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.75</v>
+        <v>1.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="T21" t="n">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>3.24</v>
       </c>
       <c r="X21" t="n">
-        <v>3.25</v>
+        <v>1.24</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AJ21" t="n">
         <v>5.25</v>
       </c>
-      <c r="AK21" s="3" t="n">
+      <c r="Z21" s="3" t="n">
         <v>45966.60416666666</v>
       </c>
     </row>
@@ -3258,76 +2463,39 @@
         <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.85</v>
+        <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>4.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>1.14</v>
       </c>
       <c r="R22" t="n">
-        <v>1.62</v>
+        <v>3.21</v>
       </c>
       <c r="S22" t="n">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ22" t="n">
         <v>2.7</v>
       </c>
-      <c r="AK22" s="3" t="n">
+      <c r="Z22" s="3" t="n">
         <v>45966.60416666666</v>
       </c>
     </row>
@@ -3387,76 +2555,39 @@
         <v>1.45</v>
       </c>
       <c r="O23" t="n">
-        <v>8.51</v>
+        <v>1.6</v>
       </c>
       <c r="P23" t="n">
-        <v>1.81</v>
+        <v>3.9</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R23" t="n">
         <v>2.35</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.6</v>
-      </c>
       <c r="S23" t="n">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="T23" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
         <v>3.9</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Y23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ23" t="n">
         <v>1.43</v>
       </c>
-      <c r="AK23" s="3" t="n">
+      <c r="Z23" s="3" t="n">
         <v>45966.60416666666</v>
       </c>
     </row>
@@ -3516,76 +2647,39 @@
         <v>1.47</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>2.77</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ24" t="n">
         <v>1.4</v>
       </c>
-      <c r="AK24" s="3" t="n">
+      <c r="Z24" s="3" t="n">
         <v>45966.61458333334</v>
       </c>
     </row>
@@ -3645,76 +2739,39 @@
         <v>1.37</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>3.85</v>
+        <v>2.57</v>
       </c>
       <c r="T25" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="U25" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AJ25" t="n">
         <v>1.35</v>
       </c>
-      <c r="AK25" s="3" t="n">
+      <c r="Z25" s="3" t="n">
         <v>45966.61458333334</v>
       </c>
     </row>
@@ -3774,76 +2831,39 @@
         <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.25</v>
+        <v>1.42</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>2.16</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ26" t="n">
         <v>2.6</v>
       </c>
-      <c r="AK26" s="3" t="n">
+      <c r="Z26" s="3" t="n">
         <v>45966.625</v>
       </c>
     </row>
@@ -3903,76 +2923,39 @@
         <v>2.71</v>
       </c>
       <c r="O27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P27" t="n">
         <v>3.5</v>
       </c>
-      <c r="P27" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>1.24</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="U27" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ27" t="n">
         <v>2</v>
       </c>
-      <c r="AK27" s="3" t="n">
+      <c r="Z27" s="3" t="n">
         <v>45966.66666666666</v>
       </c>
     </row>
@@ -4032,76 +3015,39 @@
         <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>3.52</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>1.39</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="W28" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="X28" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD28" t="n">
         <v>2</v>
       </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK28" s="3" t="n">
+      <c r="Z28" s="3" t="n">
         <v>45966.69791666666</v>
       </c>
     </row>
@@ -4161,76 +3107,39 @@
         <v>3.08</v>
       </c>
       <c r="O29" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.28</v>
+        <v>1.36</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="X29" t="n">
-        <v>2.72</v>
+        <v>1.83</v>
       </c>
       <c r="Y29" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK29" s="3" t="n">
+      <c r="Z29" s="3" t="n">
         <v>45966.69791666666</v>
       </c>
     </row>
@@ -4290,76 +3199,39 @@
         <v>2.1</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>1.38</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AJ30" t="n">
         <v>1.74</v>
       </c>
-      <c r="AK30" s="3" t="n">
+      <c r="Z30" s="3" t="n">
         <v>45966.69791666666</v>
       </c>
     </row>
@@ -4419,76 +3291,39 @@
         <v>3.1</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.19</v>
+        <v>1.36</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.98</v>
       </c>
       <c r="S31" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ31" t="n">
         <v>2.2</v>
       </c>
-      <c r="AK31" s="3" t="n">
+      <c r="Z31" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -4548,76 +3383,39 @@
         <v>5.8</v>
       </c>
       <c r="O32" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="P32" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>1.48</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="S32" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="T32" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="U32" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="W32" t="n">
-        <v>1.23</v>
+        <v>2.8</v>
       </c>
       <c r="X32" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ32" t="n">
         <v>3.35</v>
       </c>
-      <c r="AK32" s="3" t="n">
+      <c r="Z32" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -4677,76 +3475,39 @@
         <v>29</v>
       </c>
       <c r="O33" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>4.1</v>
+        <v>1.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>2.05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4.11</v>
       </c>
       <c r="T33" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="U33" t="n">
-        <v>2.05</v>
+        <v>1.46</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.06</v>
+        <v>10</v>
       </c>
       <c r="X33" t="n">
-        <v>8.5</v>
+        <v>1.08</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ33" t="n">
         <v>7</v>
       </c>
-      <c r="AK33" s="3" t="n">
+      <c r="Z33" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -4806,76 +3567,39 @@
         <v>6</v>
       </c>
       <c r="O34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1.73</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5.25</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>4.05</v>
+        <v>2.78</v>
       </c>
       <c r="T34" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="U34" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>2.52</v>
       </c>
       <c r="X34" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ34" t="n">
         <v>3</v>
       </c>
-      <c r="AK34" s="3" t="n">
+      <c r="Z34" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -4935,76 +3659,39 @@
         <v>3.37</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="S35" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.53</v>
+        <v>1.61</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>2.39</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W35" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="X35" t="n">
-        <v>4.2</v>
+        <v>1.66</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AJ35" t="n">
         <v>2.25</v>
       </c>
-      <c r="AK35" s="3" t="n">
+      <c r="Z35" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -5064,76 +3751,39 @@
         <v>2.03</v>
       </c>
       <c r="O36" t="n">
-        <v>3.01</v>
+        <v>1.23</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="R36" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="S36" t="n">
-        <v>3.94</v>
+        <v>2.35</v>
       </c>
       <c r="T36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X36" t="n">
         <v>2.05</v>
       </c>
-      <c r="U36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X36" t="n">
-        <v>6</v>
-      </c>
       <c r="Y36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB36" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AK36" s="3" t="n">
+      <c r="Z36" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -5193,76 +3843,39 @@
         <v>1.52</v>
       </c>
       <c r="O37" t="n">
-        <v>4.75</v>
+        <v>1.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.59</v>
+        <v>1.88</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>4.5</v>
+        <v>3.21</v>
       </c>
       <c r="T37" t="n">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.88</v>
+        <v>2.99</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>8.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ37" t="n">
         <v>1.44</v>
       </c>
-      <c r="AK37" s="3" t="n">
+      <c r="Z37" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -5322,76 +3935,39 @@
         <v>3.29</v>
       </c>
       <c r="O38" t="n">
-        <v>2.65</v>
+        <v>1.29</v>
       </c>
       <c r="P38" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.62</v>
+        <v>1.56</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="T38" t="n">
-        <v>2.42</v>
+        <v>1.58</v>
       </c>
       <c r="U38" t="n">
-        <v>1.56</v>
+        <v>2.46</v>
       </c>
       <c r="V38" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="X38" t="n">
-        <v>4.5</v>
+        <v>1.72</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z38" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK38" s="3" t="n">
+      <c r="Z38" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -5451,76 +4027,39 @@
         <v>6.2</v>
       </c>
       <c r="O39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S39" t="n">
         <v>2.02</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
       <c r="T39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W39" t="n">
         <v>2.5</v>
       </c>
-      <c r="U39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X39" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ39" t="n">
         <v>3.16</v>
       </c>
-      <c r="AK39" s="3" t="n">
+      <c r="Z39" s="3" t="n">
         <v>45966.72916666666</v>
       </c>
     </row>
@@ -5580,76 +4119,39 @@
         <v>2.75</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>1.47</v>
       </c>
       <c r="P40" t="n">
-        <v>1.94</v>
+        <v>3.22</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.55</v>
+        <v>1.29</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>2.35</v>
       </c>
       <c r="S40" t="n">
-        <v>2.66</v>
+        <v>1.6</v>
       </c>
       <c r="T40" t="n">
-        <v>3.22</v>
+        <v>1.96</v>
       </c>
       <c r="U40" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="V40" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="W40" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X40" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ40" t="n">
         <v>2.1</v>
       </c>
-      <c r="AK40" s="3" t="n">
+      <c r="Z40" s="3" t="n">
         <v>45966.79166666666</v>
       </c>
     </row>
@@ -5709,76 +4211,39 @@
         <v>2.94</v>
       </c>
       <c r="O41" t="n">
-        <v>3.25</v>
+        <v>1.47</v>
       </c>
       <c r="P41" t="n">
-        <v>1.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.16</v>
+        <v>1.3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.47</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="T41" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="V41" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="W41" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X41" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI41" t="n">
         <v>2.05</v>
       </c>
-      <c r="AJ41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK41" s="3" t="n">
+      <c r="Z41" s="3" t="n">
         <v>45966.79166666666</v>
       </c>
     </row>
@@ -5838,76 +4303,39 @@
         <v>3.67</v>
       </c>
       <c r="O42" t="n">
-        <v>2.36</v>
+        <v>1.41</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>1.37</v>
       </c>
       <c r="R42" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="S42" t="n">
-        <v>2.99</v>
+        <v>1.78</v>
       </c>
       <c r="T42" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.37</v>
+        <v>1.82</v>
       </c>
       <c r="V42" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="W42" t="n">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="X42" t="n">
-        <v>3.2</v>
+        <v>1.66</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AJ42" t="n">
         <v>2.5</v>
       </c>
-      <c r="AK42" s="3" t="n">
+      <c r="Z42" s="3" t="n">
         <v>45966.8125</v>
       </c>
     </row>
@@ -5967,76 +4395,39 @@
         <v>3.3</v>
       </c>
       <c r="O43" t="n">
-        <v>2.72</v>
+        <v>1.51</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>3.27</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.82</v>
+        <v>1.33</v>
       </c>
       <c r="R43" t="n">
-        <v>1.51</v>
+        <v>2.35</v>
       </c>
       <c r="S43" t="n">
-        <v>2.62</v>
+        <v>1.6</v>
       </c>
       <c r="T43" t="n">
-        <v>3.27</v>
+        <v>1.95</v>
       </c>
       <c r="U43" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V43" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="W43" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="X43" t="n">
-        <v>2.81</v>
+        <v>1.83</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ43" t="n">
         <v>2.38</v>
       </c>
-      <c r="AK43" s="3" t="n">
+      <c r="Z43" s="3" t="n">
         <v>45966.83333333334</v>
       </c>
     </row>
@@ -6096,76 +4487,39 @@
         <v>2.24</v>
       </c>
       <c r="O44" t="n">
-        <v>3.76</v>
+        <v>1.43</v>
       </c>
       <c r="P44" t="n">
-        <v>2.03</v>
+        <v>2.89</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="R44" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="S44" t="n">
-        <v>2.91</v>
+        <v>1.6</v>
       </c>
       <c r="T44" t="n">
-        <v>2.89</v>
+        <v>1.86</v>
       </c>
       <c r="U44" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="W44" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X44" t="n">
-        <v>3.34</v>
+        <v>2.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ44" t="n">
         <v>1.83</v>
       </c>
-      <c r="AK44" s="3" t="n">
+      <c r="Z44" s="3" t="n">
         <v>45966.83333333334</v>
       </c>
     </row>
@@ -6225,76 +4579,39 @@
         <v>1.84</v>
       </c>
       <c r="O45" t="n">
-        <v>4.5</v>
+        <v>1.49</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.61</v>
+        <v>1.32</v>
       </c>
       <c r="R45" t="n">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="S45" t="n">
-        <v>2.48</v>
+        <v>1.57</v>
       </c>
       <c r="T45" t="n">
-        <v>3.4</v>
+        <v>2.06</v>
       </c>
       <c r="U45" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="V45" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="X45" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AJ45" t="n">
         <v>1.72</v>
       </c>
-      <c r="AK45" s="3" t="n">
+      <c r="Z45" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,60 +508,75 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Odd_H_HT</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_HT</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_marcar_prim_H</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_marcar_prim_A</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -623,39 +638,48 @@
         <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>1.95</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1.44</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>3.1</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="AC2" s="3" t="n">
         <v>45966.33333333334</v>
       </c>
     </row>
@@ -715,39 +739,48 @@
         <v>2.33</v>
       </c>
       <c r="O3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.34</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>1.4</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>1.81</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>1.89</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>1.7</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>2.05</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>1.3</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>1.25</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z3" s="3" t="n">
+      <c r="AC3" s="3" t="n">
         <v>45966.33333333334</v>
       </c>
     </row>
@@ -807,39 +840,48 @@
         <v>2.43</v>
       </c>
       <c r="O4" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.46</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>1.27</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>2.25</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>1.58</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>1.87</v>
       </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
         <v>1.8</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>1.28</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Z4" t="n">
         <v>1.34</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>2</v>
       </c>
-      <c r="Z4" s="3" t="n">
+      <c r="AC4" s="3" t="n">
         <v>45966.33333333334</v>
       </c>
     </row>
@@ -899,39 +941,48 @@
         <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.47</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
         <v>1.48</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.61</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>3</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="AC5" s="3" t="n">
         <v>45966.375</v>
       </c>
     </row>
@@ -991,39 +1042,48 @@
         <v>3.4</v>
       </c>
       <c r="O6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.35</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>2.56</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>1.41</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>1.8</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>2.01</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>1.7</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>2.15</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>1.21</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>1.76</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>1.77</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>2.35</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="AC6" s="3" t="n">
         <v>45966.375</v>
       </c>
     </row>
@@ -1115,7 +1175,16 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="n">
         <v>45966.375</v>
       </c>
     </row>
@@ -1175,39 +1244,48 @@
         <v>1.82</v>
       </c>
       <c r="O8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.36</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>1.36</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>1.9</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>1.7</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>1.85</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>1.91</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>1.91</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>1.18</v>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="3" t="n">
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3" t="n">
         <v>45966.39583333334</v>
       </c>
     </row>
@@ -1267,39 +1345,48 @@
         <v>2.99</v>
       </c>
       <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.5</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>1.29</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>2.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>1.44</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>1.73</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>1.32</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>1.55</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>1.76</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>2.47</v>
       </c>
-      <c r="Z9" s="3" t="n">
+      <c r="AC9" s="3" t="n">
         <v>45966.41666666666</v>
       </c>
     </row>
@@ -1359,39 +1446,48 @@
         <v>1.98</v>
       </c>
       <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.62</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>3.58</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>1.21</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>2.25</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>1.55</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>2.71</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>1.43</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
         <v>1.35</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>1.12</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>3.1</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z10" s="3" t="n">
+      <c r="AC10" s="3" t="n">
         <v>45966.4375</v>
       </c>
     </row>
@@ -1451,39 +1547,48 @@
         <v>3.15</v>
       </c>
       <c r="O11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.68</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>4.05</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>1.16</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>3.04</v>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>1.31</v>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>2.51</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>1.49</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
         <v>1.33</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>1.22</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z11" s="3" t="n">
+      <c r="AC11" s="3" t="n">
         <v>45966.4375</v>
       </c>
     </row>
@@ -1543,39 +1648,48 @@
         <v>3.25</v>
       </c>
       <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.68</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>3.86</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>1.18</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>2.81</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>1.36</v>
       </c>
-      <c r="T12" t="n">
+      <c r="W12" t="n">
         <v>2.43</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>1.52</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
         <v>1.43</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>1.61</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>1.95</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>2.45</v>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="AC12" s="3" t="n">
         <v>45966.4375</v>
       </c>
     </row>
@@ -1635,39 +1749,48 @@
         <v>2.3</v>
       </c>
       <c r="O13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.56</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>3.58</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>1.25</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>2.35</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>1.52</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>2.48</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>1.5</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>1.36</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>1.75</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>1.9</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="AC13" s="3" t="n">
         <v>45966.4375</v>
       </c>
     </row>
@@ -1727,39 +1850,48 @@
         <v>4.9</v>
       </c>
       <c r="O14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.44</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>1.31</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>2.17</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>1.7</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>2.14</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>1.71</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>1.27</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Z14" t="n">
         <v>2.33</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AA14" t="n">
         <v>1.57</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>2.94</v>
       </c>
-      <c r="Z14" s="3" t="n">
+      <c r="AC14" s="3" t="n">
         <v>45966.45833333334</v>
       </c>
     </row>
@@ -1851,7 +1983,16 @@
       <c r="Y15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="n">
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="n">
         <v>45966.5</v>
       </c>
     </row>
@@ -1911,39 +2052,48 @@
         <v>1.24</v>
       </c>
       <c r="O16" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.33</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>2.88</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>1.36</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>1.86</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>1.8</v>
       </c>
-      <c r="T16" t="n">
+      <c r="W16" t="n">
         <v>3.2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
         <v>1.33</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
         <v>1.11</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
         <v>1.04</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
         <v>4.5</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" s="3" t="n">
+      <c r="AC16" s="3" t="n">
         <v>45966.54166666666</v>
       </c>
     </row>
@@ -2003,39 +2153,48 @@
         <v>3.1</v>
       </c>
       <c r="O17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.33</v>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>2.43</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="T17" t="n">
         <v>1.43</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>1.87</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>1.95</v>
       </c>
-      <c r="T17" t="n">
+      <c r="W17" t="n">
         <v>1.67</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>2.08</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>1.24</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
         <v>1.7</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>1.8</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z17" s="3" t="n">
+      <c r="AC17" s="3" t="n">
         <v>45966.54166666666</v>
       </c>
     </row>
@@ -2095,39 +2254,48 @@
         <v>1.48</v>
       </c>
       <c r="O18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.36</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
         <v>1.42</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>1.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>1.9</v>
       </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
         <v>2.09</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>1.63</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
         <v>2.8</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
         <v>1.07</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AA18" t="n">
         <v>3.85</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z18" s="3" t="n">
+      <c r="AC18" s="3" t="n">
         <v>45966.54166666666</v>
       </c>
     </row>
@@ -2187,39 +2355,48 @@
         <v>6.9</v>
       </c>
       <c r="O19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.38</v>
       </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="T19" t="n">
         <v>1.38</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>1.72</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>2.3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>1.5</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>1.14</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>3.1</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AA19" t="n">
         <v>1.33</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>4.2</v>
       </c>
-      <c r="Z19" s="3" t="n">
+      <c r="AC19" s="3" t="n">
         <v>45966.58333333334</v>
       </c>
     </row>
@@ -2279,39 +2456,48 @@
         <v>6.7</v>
       </c>
       <c r="O20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.61</v>
       </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
         <v>3.58</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="T20" t="n">
         <v>1.25</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>2.25</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>1.57</v>
       </c>
-      <c r="T20" t="n">
+      <c r="W20" t="n">
         <v>2.4</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>1.45</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>1.15</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
         <v>1.98</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AA20" t="n">
         <v>1.57</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>3.2</v>
       </c>
-      <c r="Z20" s="3" t="n">
+      <c r="AC20" s="3" t="n">
         <v>45966.60416666666</v>
       </c>
     </row>
@@ -2371,39 +2557,48 @@
         <v>12</v>
       </c>
       <c r="O21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.37</v>
       </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
         <v>3.18</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>1.35</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>1.9</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>1.8</v>
       </c>
-      <c r="T21" t="n">
+      <c r="W21" t="n">
         <v>2.87</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>1.43</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>1.18</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
         <v>3.24</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AA21" t="n">
         <v>1.24</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
         <v>5.25</v>
       </c>
-      <c r="Z21" s="3" t="n">
+      <c r="AC21" s="3" t="n">
         <v>45966.60416666666</v>
       </c>
     </row>
@@ -2463,39 +2658,48 @@
         <v>4.2</v>
       </c>
       <c r="O22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.62</v>
       </c>
-      <c r="P22" t="n">
+      <c r="S22" t="n">
         <v>4.33</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="T22" t="n">
         <v>1.14</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>3.21</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>1.3</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>2.5</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>1.42</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>1.36</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
         <v>1.6</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AA22" t="n">
         <v>1.9</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>2.7</v>
       </c>
-      <c r="Z22" s="3" t="n">
+      <c r="AC22" s="3" t="n">
         <v>45966.60416666666</v>
       </c>
     </row>
@@ -2555,39 +2759,48 @@
         <v>1.45</v>
       </c>
       <c r="O23" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.6</v>
       </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
         <v>3.9</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="T23" t="n">
         <v>1.15</v>
       </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>2.35</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>1.53</v>
       </c>
-      <c r="T23" t="n">
+      <c r="W23" t="n">
         <v>3.11</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>1.29</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>1.36</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
         <v>1.04</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AA23" t="n">
         <v>3.9</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z23" s="3" t="n">
+      <c r="AC23" s="3" t="n">
         <v>45966.60416666666</v>
       </c>
     </row>
@@ -2647,39 +2860,48 @@
         <v>1.47</v>
       </c>
       <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.3</v>
       </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="T24" t="n">
         <v>1.5</v>
       </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
         <v>1.73</v>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>2.1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="W24" t="n">
         <v>1.86</v>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
         <v>2</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
         <v>2.77</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Z24" t="n">
         <v>1.12</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
         <v>3</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z24" s="3" t="n">
+      <c r="AC24" s="3" t="n">
         <v>45966.61458333334</v>
       </c>
     </row>
@@ -2739,39 +2961,48 @@
         <v>1.37</v>
       </c>
       <c r="O25" t="n">
+        <v>7</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.25</v>
       </c>
-      <c r="P25" t="n">
+      <c r="S25" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="T25" t="n">
         <v>1.65</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>1.47</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>2.57</v>
       </c>
-      <c r="T25" t="n">
+      <c r="W25" t="n">
         <v>1.73</v>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>2</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>1.18</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
         <v>1.09</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
         <v>3.3</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z25" s="3" t="n">
+      <c r="AC25" s="3" t="n">
         <v>45966.61458333334</v>
       </c>
     </row>
@@ -2831,39 +3062,48 @@
         <v>4</v>
       </c>
       <c r="O26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.36</v>
       </c>
-      <c r="P26" t="n">
+      <c r="S26" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="T26" t="n">
         <v>1.42</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
         <v>2.1</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>1.65</v>
       </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
         <v>1.83</v>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>1.88</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
         <v>1.19</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Z26" t="n">
         <v>2.16</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
         <v>1.57</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z26" s="3" t="n">
+      <c r="AC26" s="3" t="n">
         <v>45966.625</v>
       </c>
     </row>
@@ -2923,39 +3163,48 @@
         <v>2.71</v>
       </c>
       <c r="O27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.57</v>
       </c>
-      <c r="P27" t="n">
+      <c r="S27" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="T27" t="n">
         <v>1.24</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
         <v>2.3</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>1.62</v>
       </c>
-      <c r="T27" t="n">
+      <c r="W27" t="n">
         <v>2.17</v>
       </c>
-      <c r="U27" t="n">
+      <c r="X27" t="n">
         <v>1.75</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>1.41</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
         <v>1.38</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AA27" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
         <v>2</v>
       </c>
-      <c r="Z27" s="3" t="n">
+      <c r="AC27" s="3" t="n">
         <v>45966.66666666666</v>
       </c>
     </row>
@@ -3015,39 +3264,48 @@
         <v>2.28</v>
       </c>
       <c r="O28" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.4</v>
       </c>
-      <c r="P28" t="n">
+      <c r="S28" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="T28" t="n">
         <v>1.39</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
         <v>1.89</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>1.85</v>
       </c>
-      <c r="T28" t="n">
+      <c r="W28" t="n">
         <v>1.72</v>
       </c>
-      <c r="U28" t="n">
+      <c r="X28" t="n">
         <v>2</v>
       </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
         <v>1.27</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Z28" t="n">
         <v>1.38</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AA28" t="n">
         <v>2.05</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AB28" t="n">
         <v>2</v>
       </c>
-      <c r="Z28" s="3" t="n">
+      <c r="AC28" s="3" t="n">
         <v>45966.69791666666</v>
       </c>
     </row>
@@ -3107,39 +3365,48 @@
         <v>3.08</v>
       </c>
       <c r="O29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R29" t="n">
         <v>1.45</v>
       </c>
-      <c r="P29" t="n">
+      <c r="S29" t="n">
         <v>2.88</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="T29" t="n">
         <v>1.36</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>2.3</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>1.6</v>
       </c>
-      <c r="T29" t="n">
+      <c r="W29" t="n">
         <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.62</v>
       </c>
       <c r="X29" t="n">
         <v>1.83</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z29" s="3" t="n">
+      <c r="AC29" s="3" t="n">
         <v>45966.69791666666</v>
       </c>
     </row>
@@ -3199,39 +3466,48 @@
         <v>2.1</v>
       </c>
       <c r="O30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.38</v>
       </c>
-      <c r="P30" t="n">
+      <c r="S30" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="T30" t="n">
         <v>1.4</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>1.77</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>1.98</v>
       </c>
-      <c r="T30" t="n">
+      <c r="W30" t="n">
         <v>1.73</v>
       </c>
-      <c r="U30" t="n">
+      <c r="X30" t="n">
         <v>1.95</v>
       </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
         <v>1.28</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Z30" t="n">
         <v>1.27</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AA30" t="n">
         <v>2.23</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AB30" t="n">
         <v>1.74</v>
       </c>
-      <c r="Z30" s="3" t="n">
+      <c r="AC30" s="3" t="n">
         <v>45966.69791666666</v>
       </c>
     </row>
@@ -3291,39 +3567,48 @@
         <v>3.1</v>
       </c>
       <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.42</v>
       </c>
-      <c r="P31" t="n">
+      <c r="S31" t="n">
         <v>2.88</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="T31" t="n">
         <v>1.36</v>
       </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>1.98</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>1.77</v>
       </c>
-      <c r="T31" t="n">
+      <c r="W31" t="n">
         <v>1.8</v>
       </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
         <v>1.93</v>
       </c>
-      <c r="V31" t="n">
+      <c r="Y31" t="n">
         <v>1.38</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Z31" t="n">
         <v>1.45</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AA31" t="n">
         <v>1.95</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AB31" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z31" s="3" t="n">
+      <c r="AC31" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -3383,39 +3668,48 @@
         <v>5.8</v>
       </c>
       <c r="O32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.36</v>
       </c>
-      <c r="P32" t="n">
+      <c r="S32" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="T32" t="n">
         <v>1.48</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
         <v>1.79</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>1.94</v>
       </c>
-      <c r="T32" t="n">
+      <c r="W32" t="n">
         <v>1.95</v>
       </c>
-      <c r="U32" t="n">
+      <c r="X32" t="n">
         <v>1.75</v>
       </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
         <v>1.16</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Z32" t="n">
         <v>2.8</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AA32" t="n">
         <v>1.4</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AB32" t="n">
         <v>3.35</v>
       </c>
-      <c r="Z32" s="3" t="n">
+      <c r="AC32" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -3475,39 +3769,48 @@
         <v>29</v>
       </c>
       <c r="O33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>23</v>
+      </c>
+      <c r="R33" t="n">
         <v>1.15</v>
       </c>
-      <c r="P33" t="n">
+      <c r="S33" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="T33" t="n">
         <v>2.05</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
         <v>1.21</v>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
         <v>4.11</v>
       </c>
-      <c r="T33" t="n">
+      <c r="W33" t="n">
         <v>2.62</v>
       </c>
-      <c r="U33" t="n">
+      <c r="X33" t="n">
         <v>1.46</v>
       </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
         <v>1.01</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Z33" t="n">
         <v>10</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AA33" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AB33" t="n">
         <v>7</v>
       </c>
-      <c r="Z33" s="3" t="n">
+      <c r="AC33" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -3567,39 +3870,48 @@
         <v>6</v>
       </c>
       <c r="O34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R34" t="n">
         <v>1.22</v>
       </c>
-      <c r="P34" t="n">
+      <c r="S34" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="T34" t="n">
         <v>1.73</v>
       </c>
-      <c r="R34" t="n">
+      <c r="U34" t="n">
         <v>1.41</v>
       </c>
-      <c r="S34" t="n">
+      <c r="V34" t="n">
         <v>2.78</v>
       </c>
-      <c r="T34" t="n">
+      <c r="W34" t="n">
         <v>1.53</v>
       </c>
-      <c r="U34" t="n">
+      <c r="X34" t="n">
         <v>2.3</v>
       </c>
-      <c r="V34" t="n">
+      <c r="Y34" t="n">
         <v>1.15</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Z34" t="n">
         <v>2.52</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AA34" t="n">
         <v>1.4</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AB34" t="n">
         <v>3</v>
       </c>
-      <c r="Z34" s="3" t="n">
+      <c r="AC34" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -3659,39 +3971,48 @@
         <v>3.37</v>
       </c>
       <c r="O35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4</v>
+      </c>
+      <c r="R35" t="n">
         <v>1.3</v>
       </c>
-      <c r="P35" t="n">
+      <c r="S35" t="n">
         <v>2.53</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="T35" t="n">
         <v>1.53</v>
       </c>
-      <c r="R35" t="n">
+      <c r="U35" t="n">
         <v>1.73</v>
       </c>
-      <c r="S35" t="n">
+      <c r="V35" t="n">
         <v>2.1</v>
       </c>
-      <c r="T35" t="n">
+      <c r="W35" t="n">
         <v>1.61</v>
       </c>
-      <c r="U35" t="n">
+      <c r="X35" t="n">
         <v>2.39</v>
       </c>
-      <c r="V35" t="n">
+      <c r="Y35" t="n">
         <v>1.22</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Z35" t="n">
         <v>1.91</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AA35" t="n">
         <v>1.66</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AB35" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z35" s="3" t="n">
+      <c r="AC35" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -3751,39 +4072,48 @@
         <v>2.03</v>
       </c>
       <c r="O36" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R36" t="n">
         <v>1.23</v>
       </c>
-      <c r="P36" t="n">
+      <c r="S36" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="T36" t="n">
         <v>1.73</v>
       </c>
-      <c r="R36" t="n">
+      <c r="U36" t="n">
         <v>1.6</v>
       </c>
-      <c r="S36" t="n">
+      <c r="V36" t="n">
         <v>2.35</v>
       </c>
-      <c r="T36" t="n">
+      <c r="W36" t="n">
         <v>1.4</v>
       </c>
-      <c r="U36" t="n">
+      <c r="X36" t="n">
         <v>2.8</v>
       </c>
-      <c r="V36" t="n">
+      <c r="Y36" t="n">
         <v>1.28</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Z36" t="n">
         <v>1.36</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AA36" t="n">
         <v>2.05</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AB36" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z36" s="3" t="n">
+      <c r="AC36" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -3843,39 +4173,48 @@
         <v>1.52</v>
       </c>
       <c r="O37" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R37" t="n">
         <v>1.2</v>
       </c>
-      <c r="P37" t="n">
+      <c r="S37" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="T37" t="n">
         <v>1.88</v>
       </c>
-      <c r="R37" t="n">
+      <c r="U37" t="n">
         <v>1.32</v>
       </c>
-      <c r="S37" t="n">
+      <c r="V37" t="n">
         <v>3.21</v>
       </c>
-      <c r="T37" t="n">
+      <c r="W37" t="n">
         <v>1.4</v>
       </c>
-      <c r="U37" t="n">
+      <c r="X37" t="n">
         <v>2.99</v>
       </c>
-      <c r="V37" t="n">
+      <c r="Y37" t="n">
         <v>1.14</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Z37" t="n">
         <v>1.12</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AA37" t="n">
         <v>2.75</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AB37" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z37" s="3" t="n">
+      <c r="AC37" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -3935,39 +4274,48 @@
         <v>3.29</v>
       </c>
       <c r="O38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R38" t="n">
         <v>1.29</v>
       </c>
-      <c r="P38" t="n">
+      <c r="S38" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="T38" t="n">
         <v>1.56</v>
       </c>
-      <c r="R38" t="n">
+      <c r="U38" t="n">
         <v>1.75</v>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
         <v>2.1</v>
       </c>
-      <c r="T38" t="n">
+      <c r="W38" t="n">
         <v>1.58</v>
       </c>
-      <c r="U38" t="n">
+      <c r="X38" t="n">
         <v>2.46</v>
       </c>
-      <c r="V38" t="n">
+      <c r="Y38" t="n">
         <v>1.24</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Z38" t="n">
         <v>1.7</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AA38" t="n">
         <v>1.72</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AB38" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z38" s="3" t="n">
+      <c r="AC38" s="3" t="n">
         <v>45966.70833333334</v>
       </c>
     </row>
@@ -4027,39 +4375,48 @@
         <v>6.2</v>
       </c>
       <c r="O39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.35</v>
       </c>
-      <c r="P39" t="n">
+      <c r="S39" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="T39" t="n">
         <v>1.48</v>
       </c>
-      <c r="R39" t="n">
+      <c r="U39" t="n">
         <v>1.87</v>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
         <v>2.02</v>
       </c>
-      <c r="T39" t="n">
+      <c r="W39" t="n">
         <v>1.9</v>
       </c>
-      <c r="U39" t="n">
+      <c r="X39" t="n">
         <v>1.8</v>
       </c>
-      <c r="V39" t="n">
+      <c r="Y39" t="n">
         <v>1.19</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Z39" t="n">
         <v>2.5</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AA39" t="n">
         <v>1.4</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AB39" t="n">
         <v>3.16</v>
       </c>
-      <c r="Z39" s="3" t="n">
+      <c r="AC39" s="3" t="n">
         <v>45966.72916666666</v>
       </c>
     </row>
@@ -4119,39 +4476,48 @@
         <v>2.75</v>
       </c>
       <c r="O40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.47</v>
       </c>
-      <c r="P40" t="n">
+      <c r="S40" t="n">
         <v>3.22</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="T40" t="n">
         <v>1.29</v>
       </c>
-      <c r="R40" t="n">
+      <c r="U40" t="n">
         <v>2.35</v>
       </c>
-      <c r="S40" t="n">
+      <c r="V40" t="n">
         <v>1.6</v>
       </c>
-      <c r="T40" t="n">
+      <c r="W40" t="n">
         <v>1.96</v>
       </c>
-      <c r="U40" t="n">
+      <c r="X40" t="n">
         <v>1.83</v>
       </c>
-      <c r="V40" t="n">
+      <c r="Y40" t="n">
         <v>1.3</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Z40" t="n">
         <v>1.5</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AA40" t="n">
         <v>1.95</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AB40" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z40" s="3" t="n">
+      <c r="AC40" s="3" t="n">
         <v>45966.79166666666</v>
       </c>
     </row>
@@ -4211,39 +4577,48 @@
         <v>2.94</v>
       </c>
       <c r="O41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R41" t="n">
         <v>1.47</v>
       </c>
-      <c r="P41" t="n">
+      <c r="S41" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="T41" t="n">
         <v>1.3</v>
       </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
         <v>2.13</v>
       </c>
-      <c r="S41" t="n">
+      <c r="V41" t="n">
         <v>1.63</v>
       </c>
-      <c r="T41" t="n">
+      <c r="W41" t="n">
         <v>1.91</v>
       </c>
-      <c r="U41" t="n">
+      <c r="X41" t="n">
         <v>1.76</v>
       </c>
-      <c r="V41" t="n">
+      <c r="Y41" t="n">
         <v>1.31</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Z41" t="n">
         <v>1.41</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AA41" t="n">
         <v>2.05</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AB41" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z41" s="3" t="n">
+      <c r="AC41" s="3" t="n">
         <v>45966.79166666666</v>
       </c>
     </row>
@@ -4303,39 +4678,48 @@
         <v>3.67</v>
       </c>
       <c r="O42" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4</v>
+      </c>
+      <c r="R42" t="n">
         <v>1.41</v>
       </c>
-      <c r="P42" t="n">
+      <c r="S42" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="T42" t="n">
         <v>1.37</v>
       </c>
-      <c r="R42" t="n">
+      <c r="U42" t="n">
         <v>1.92</v>
       </c>
-      <c r="S42" t="n">
+      <c r="V42" t="n">
         <v>1.78</v>
       </c>
-      <c r="T42" t="n">
+      <c r="W42" t="n">
         <v>1.8</v>
       </c>
-      <c r="U42" t="n">
+      <c r="X42" t="n">
         <v>1.82</v>
       </c>
-      <c r="V42" t="n">
+      <c r="Y42" t="n">
         <v>1.22</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Z42" t="n">
         <v>1.93</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AA42" t="n">
         <v>1.66</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AB42" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z42" s="3" t="n">
+      <c r="AC42" s="3" t="n">
         <v>45966.8125</v>
       </c>
     </row>
@@ -4395,39 +4779,48 @@
         <v>3.3</v>
       </c>
       <c r="O43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R43" t="n">
         <v>1.51</v>
       </c>
-      <c r="P43" t="n">
+      <c r="S43" t="n">
         <v>3.27</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="T43" t="n">
         <v>1.33</v>
       </c>
-      <c r="R43" t="n">
+      <c r="U43" t="n">
         <v>2.35</v>
       </c>
-      <c r="S43" t="n">
+      <c r="V43" t="n">
         <v>1.6</v>
       </c>
-      <c r="T43" t="n">
+      <c r="W43" t="n">
         <v>1.95</v>
       </c>
-      <c r="U43" t="n">
+      <c r="X43" t="n">
         <v>1.73</v>
       </c>
-      <c r="V43" t="n">
+      <c r="Y43" t="n">
         <v>1.27</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Z43" t="n">
         <v>1.67</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AA43" t="n">
         <v>1.83</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AB43" t="n">
         <v>2.38</v>
       </c>
-      <c r="Z43" s="3" t="n">
+      <c r="AC43" s="3" t="n">
         <v>45966.83333333334</v>
       </c>
     </row>
@@ -4487,39 +4880,48 @@
         <v>2.24</v>
       </c>
       <c r="O44" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R44" t="n">
         <v>1.43</v>
       </c>
-      <c r="P44" t="n">
+      <c r="S44" t="n">
         <v>2.89</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="T44" t="n">
         <v>1.38</v>
       </c>
-      <c r="R44" t="n">
+      <c r="U44" t="n">
         <v>2.35</v>
       </c>
-      <c r="S44" t="n">
+      <c r="V44" t="n">
         <v>1.6</v>
       </c>
-      <c r="T44" t="n">
+      <c r="W44" t="n">
         <v>1.86</v>
       </c>
-      <c r="U44" t="n">
+      <c r="X44" t="n">
         <v>1.89</v>
       </c>
-      <c r="V44" t="n">
+      <c r="Y44" t="n">
         <v>1.61</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Z44" t="n">
         <v>1.29</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AA44" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AB44" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z44" s="3" t="n">
+      <c r="AC44" s="3" t="n">
         <v>45966.83333333334</v>
       </c>
     </row>
@@ -4579,39 +4981,48 @@
         <v>1.84</v>
       </c>
       <c r="O45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R45" t="n">
         <v>1.49</v>
       </c>
-      <c r="P45" t="n">
+      <c r="S45" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="T45" t="n">
         <v>1.32</v>
       </c>
-      <c r="R45" t="n">
+      <c r="U45" t="n">
         <v>2.4</v>
       </c>
-      <c r="S45" t="n">
+      <c r="V45" t="n">
         <v>1.57</v>
       </c>
-      <c r="T45" t="n">
+      <c r="W45" t="n">
         <v>2.06</v>
       </c>
-      <c r="U45" t="n">
+      <c r="X45" t="n">
         <v>1.66</v>
       </c>
-      <c r="V45" t="n">
+      <c r="Y45" t="n">
         <v>1.25</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Z45" t="n">
         <v>1.16</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AA45" t="n">
         <v>2.66</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AB45" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z45" s="3" t="n">
+      <c r="AC45" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,81 +603,81 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="M2" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>1.98</v>
       </c>
       <c r="O2" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="U2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.7</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC2" s="3" t="n">
         <v>45966.33333333334</v>
@@ -704,16 +704,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -726,59 +726,59 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.73</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>4.51</v>
       </c>
       <c r="N3" t="n">
-        <v>2.33</v>
+        <v>6.82</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>1.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.57</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>3.1</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>45966.33333333334</v>
@@ -817,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -840,40 +840,40 @@
         <v>2.43</v>
       </c>
       <c r="O4" t="n">
-        <v>3.73</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
         <v>3.2</v>
       </c>
       <c r="T4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.27</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z4" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
         <v>2.2</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,81 +906,81 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U5" t="n">
-        <v>2.47</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>45966.375</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1033,55 +1033,55 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>45966.375</v>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1134,58 +1134,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>45966.375</v>
+        <v>45966.39583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1235,58 +1235,58 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.84</v>
+        <v>2.24</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>2.79</v>
       </c>
       <c r="N8" t="n">
-        <v>1.82</v>
+        <v>2.99</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>4.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>45966.39583333334</v>
+        <v>45966.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1336,58 +1336,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="M9" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AB9" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>45966.41666666666</v>
+        <v>45966.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1437,55 +1437,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.95</v>
+        <v>1.69</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>4.76</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>2.41</v>
       </c>
       <c r="P10" t="n">
         <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.31</v>
+        <v>4.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="U10" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="X10" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>2.37</v>
       </c>
       <c r="AC10" s="3" t="n">
         <v>45966.4375</v>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1538,55 +1538,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.71</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
-        <v>4.3</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.05</v>
+        <v>2.31</v>
       </c>
       <c r="R11" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="U11" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>2.51</v>
+        <v>2.71</v>
       </c>
       <c r="X11" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" s="3" t="n">
         <v>45966.4375</v>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1639,55 +1639,55 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W12" t="n">
         <v>2.3</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.43</v>
-      </c>
       <c r="X12" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" s="3" t="n">
         <v>45966.4375</v>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1740,58 +1740,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.35</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>5.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="T13" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="U13" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="V13" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="W13" t="n">
-        <v>2.48</v>
+        <v>1.99</v>
       </c>
       <c r="X13" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.37</v>
+        <v>2.94</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>45966.4375</v>
+        <v>45966.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1841,58 +1841,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>4.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>4.9</v>
+        <v>1.77</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>5.95</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.95</v>
+        <v>2.47</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="U14" t="n">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="X14" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.33</v>
+        <v>1.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>45966.45833333334</v>
+        <v>45966.5</v>
       </c>
     </row>
     <row r="15">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1942,58 +1942,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>45966.5</v>
+        <v>45966.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2043,55 +2043,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.7</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
-        <v>11.4</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.36</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.25</v>
       </c>
       <c r="AC16" s="3" t="n">
         <v>45966.54166666666</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2140,62 +2140,62 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>6.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.64</v>
+        <v>1.82</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.65</v>
+        <v>8.1</v>
       </c>
       <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.33</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2245,58 +2245,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.48</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>6.5</v>
+        <v>2.53</v>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>6.01</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>3.74</v>
       </c>
       <c r="T18" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="X18" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.07</v>
+        <v>1.86</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>45966.54166666666</v>
+        <v>45966.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2346,58 +2346,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="N19" t="n">
-        <v>6.9</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.6</v>
+        <v>10.96</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="X19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>45966.58333333334</v>
+        <v>45966.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2456,22 +2456,22 @@
         <v>6.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.03</v>
+        <v>5.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="T20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="U20" t="n">
         <v>2.25</v>
@@ -2480,16 +2480,16 @@
         <v>1.57</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="X20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
         <v>1.57</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2548,55 +2548,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>7.9</v>
       </c>
       <c r="M21" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>1.45</v>
       </c>
       <c r="O21" t="n">
-        <v>1.77</v>
+        <v>7.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.75</v>
+        <v>2.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="S21" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="V21" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.43</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>5.25</v>
       </c>
       <c r="AC21" s="3" t="n">
         <v>45966.60416666666</v>
@@ -2667,13 +2667,13 @@
         <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="U22" t="n">
         <v>3.21</v>
@@ -2682,16 +2682,16 @@
         <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="X22" t="n">
         <v>1.42</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA22" t="n">
         <v>1.9</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2750,58 +2750,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="O23" t="n">
-        <v>8.51</v>
+        <v>7</v>
       </c>
       <c r="P23" t="n">
-        <v>1.81</v>
+        <v>2.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="U23" t="n">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>1.53</v>
+        <v>2.57</v>
       </c>
       <c r="W23" t="n">
-        <v>3.11</v>
+        <v>1.77</v>
       </c>
       <c r="X23" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>45966.60416666666</v>
+        <v>45966.61458333334</v>
       </c>
     </row>
     <row r="24">
@@ -2860,16 +2860,16 @@
         <v>1.47</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
         <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
         <v>2.45</v>
@@ -2884,16 +2884,16 @@
         <v>2.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AA24" t="n">
         <v>3</v>
@@ -2911,12 +2911,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2952,58 +2952,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>7</v>
+        <v>2.88</v>
       </c>
       <c r="M25" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>1.37</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T25" t="n">
         <v>1.25</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.65</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>2.56</v>
       </c>
       <c r="V25" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="X25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AC25" s="3" t="n">
-        <v>45966.61458333334</v>
+        <v>45966.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3012,27 +3012,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3053,58 +3053,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.76</v>
+        <v>3.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
         <v>1.42</v>
       </c>
       <c r="U26" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="V26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.65</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.83</v>
-      </c>
       <c r="X26" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.16</v>
+        <v>1.36</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="AC26" s="3" t="n">
-        <v>45966.625</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3154,58 +3154,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="N27" t="n">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="T27" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="U27" t="n">
         <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W27" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="X27" t="n">
         <v>1.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB27" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2</v>
-      </c>
       <c r="AC27" s="3" t="n">
-        <v>45966.66666666666</v>
+        <v>45966.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3264,22 +3264,22 @@
         <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
@@ -3288,16 +3288,16 @@
         <v>1.85</v>
       </c>
       <c r="W28" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AA28" t="n">
         <v>2.05</v>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3356,58 +3356,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.28</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="T29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.36</v>
       </c>
-      <c r="U29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z29" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="30">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3457,58 +3457,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.25</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
-        <v>3.47</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>1.73</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="T30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AA30" t="n">
         <v>1.4</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AB30" t="n">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="AC30" s="3" t="n">
-        <v>45966.69791666666</v>
+        <v>45966.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3558,55 +3558,55 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P31" t="n">
         <v>2.3</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V31" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.77</v>
-      </c>
       <c r="W31" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="X31" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC31" s="3" t="n">
         <v>45966.70833333334</v>
@@ -3668,10 +3668,10 @@
         <v>5.8</v>
       </c>
       <c r="O32" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="P32" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
         <v>7</v>
@@ -3680,10 +3680,10 @@
         <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U32" t="n">
         <v>1.79</v>
@@ -3698,10 +3698,10 @@
         <v>1.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
         <v>1.4</v>
@@ -3772,10 +3772,10 @@
         <v>1.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R33" t="n">
         <v>1.15</v>
@@ -3784,7 +3784,7 @@
         <v>1.62</v>
       </c>
       <c r="T33" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
         <v>1.21</v>
@@ -3793,16 +3793,16 @@
         <v>4.11</v>
       </c>
       <c r="W33" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="X33" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Y33" t="n">
         <v>1.01</v>
       </c>
       <c r="Z33" t="n">
-        <v>10</v>
+        <v>16.76</v>
       </c>
       <c r="AA33" t="n">
         <v>1.08</v>
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3861,55 +3861,55 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.42</v>
+        <v>4.9</v>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>1.52</v>
       </c>
       <c r="O34" t="n">
-        <v>1.73</v>
+        <v>4.75</v>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.25</v>
+        <v>1.99</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S34" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="T34" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="U34" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
-        <v>2.78</v>
+        <v>3.21</v>
       </c>
       <c r="W34" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="X34" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.15</v>
+        <v>2.39</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.52</v>
+        <v>1.19</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="AC34" s="3" t="n">
         <v>45966.70833333334</v>
@@ -3936,12 +3936,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -3962,55 +3962,55 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S35" t="n">
         <v>2.05</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.53</v>
-      </c>
       <c r="T35" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="U35" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="V35" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="W35" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="X35" t="n">
-        <v>2.39</v>
+        <v>2.92</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="AC35" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4063,55 +4063,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.14</v>
+        <v>2.04</v>
       </c>
       <c r="M36" t="n">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="N36" t="n">
-        <v>2.03</v>
+        <v>3.29</v>
       </c>
       <c r="O36" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.54</v>
+        <v>3.56</v>
       </c>
       <c r="R36" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S36" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="T36" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="U36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.6</v>
       </c>
-      <c r="V36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" s="3" t="n">
         <v>45966.70833333334</v>
@@ -4123,27 +4123,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4164,58 +4164,58 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.9</v>
+        <v>1.55</v>
       </c>
       <c r="M37" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="N37" t="n">
-        <v>1.52</v>
+        <v>5.4</v>
       </c>
       <c r="O37" t="n">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.93</v>
+        <v>4.94</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>1.88</v>
+        <v>2.72</v>
       </c>
       <c r="T37" t="n">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="V37" t="n">
-        <v>3.21</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA37" t="n">
         <v>1.4</v>
       </c>
-      <c r="X37" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.44</v>
+        <v>3.16</v>
       </c>
       <c r="AC37" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.72916666666</v>
       </c>
     </row>
     <row r="38">
@@ -4224,27 +4224,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4265,58 +4265,58 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="M38" t="n">
-        <v>3.64</v>
+        <v>3.28</v>
       </c>
       <c r="N38" t="n">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.62</v>
+        <v>4.8</v>
       </c>
       <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.29</v>
       </c>
-      <c r="S38" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z38" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AC38" s="3" t="n">
-        <v>45966.70833333334</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="39">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4366,58 +4366,58 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.48</v>
       </c>
-      <c r="M39" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="U39" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="V39" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="W39" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="X39" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.16</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" s="3" t="n">
-        <v>45966.72916666666</v>
+        <v>45966.79166666666</v>
       </c>
     </row>
     <row r="40">
@@ -4491,7 +4491,7 @@
         <v>3.22</v>
       </c>
       <c r="T40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U40" t="n">
         <v>2.35</v>
@@ -4500,16 +4500,16 @@
         <v>1.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="X40" t="n">
         <v>1.83</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA40" t="n">
         <v>1.95</v>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4568,58 +4568,58 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M41" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.94</v>
+        <v>3.67</v>
       </c>
       <c r="O41" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="P41" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="T41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y41" t="n">
         <v>1.3</v>
       </c>
-      <c r="U41" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Z41" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AC41" s="3" t="n">
-        <v>45966.79166666666</v>
+        <v>45966.8125</v>
       </c>
     </row>
     <row r="42">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4669,58 +4669,58 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.84</v>
+        <v>2.93</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>3.67</v>
+        <v>2.24</v>
       </c>
       <c r="O42" t="n">
-        <v>2.36</v>
+        <v>3.72</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="R42" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="T42" t="n">
         <v>1.37</v>
       </c>
       <c r="U42" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="V42" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W42" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X42" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.93</v>
+        <v>1.37</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AC42" s="3" t="n">
-        <v>45966.8125</v>
+        <v>45966.83333333334</v>
       </c>
     </row>
     <row r="43">
@@ -4779,19 +4779,19 @@
         <v>3.3</v>
       </c>
       <c r="O43" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
         <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S43" t="n">
-        <v>3.27</v>
+        <v>2.88</v>
       </c>
       <c r="T43" t="n">
         <v>1.33</v>
@@ -4803,16 +4803,16 @@
         <v>1.6</v>
       </c>
       <c r="W43" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X43" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA43" t="n">
         <v>1.83</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4871,158 +4871,57 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.93</v>
+        <v>3.77</v>
       </c>
       <c r="M44" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>2.24</v>
+        <v>1.84</v>
       </c>
       <c r="O44" t="n">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="P44" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R44" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="S44" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="U44" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V44" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W44" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="X44" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC44" s="3" t="n">
-        <v>45966.83333333334</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W45" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC45" s="3" t="n">
         <v>45966.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-05.xlsx
+++ b/jogos_2025-11-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,25 +603,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -629,55 +629,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>4.51</v>
       </c>
       <c r="N2" t="n">
-        <v>1.98</v>
+        <v>6.82</v>
       </c>
       <c r="O2" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.72</v>
+        <v>3.1</v>
       </c>
       <c r="AC2" s="3" t="n">
         <v>45966.33333333334</v>
@@ -704,25 +704,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -730,55 +730,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>4.51</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>6.82</v>
+        <v>1.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <